--- a/compare/output/dscale_RenTES_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_RenTES_downscaled_SSP460.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>448592.296641</v>
+        <v>447782.343799</v>
       </c>
       <c r="F2" t="n">
-        <v>462314.660195</v>
+        <v>460398.609255</v>
       </c>
       <c r="G2" t="n">
-        <v>520734.835764</v>
+        <v>516733.045852</v>
       </c>
       <c r="H2" t="n">
-        <v>572208.509658</v>
+        <v>564202.813416</v>
       </c>
       <c r="I2" t="n">
-        <v>579342.58727</v>
+        <v>562321.855363</v>
       </c>
       <c r="J2" t="n">
         <v>130017.605211</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38521.794821</v>
+        <v>38459.015569</v>
       </c>
       <c r="F3" t="n">
-        <v>34515.858055</v>
+        <v>34390.327868</v>
       </c>
       <c r="G3" t="n">
-        <v>35006.256052</v>
+        <v>34775.689142</v>
       </c>
       <c r="H3" t="n">
-        <v>36078.769188</v>
+        <v>35655.673251</v>
       </c>
       <c r="I3" t="n">
-        <v>35861.237054</v>
+        <v>35000.790688</v>
       </c>
       <c r="J3" t="n">
         <v>13942.348962</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44842.717245</v>
+        <v>44780.929631</v>
       </c>
       <c r="F4" t="n">
-        <v>37412.704539</v>
+        <v>37301.612054</v>
       </c>
       <c r="G4" t="n">
-        <v>34349.766474</v>
+        <v>34173.579384</v>
       </c>
       <c r="H4" t="n">
-        <v>33040.916299</v>
+        <v>32750.768096</v>
       </c>
       <c r="I4" t="n">
-        <v>31796.683612</v>
+        <v>31245.139764</v>
       </c>
       <c r="J4" t="n">
         <v>18036.783417</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22006.743027</v>
+        <v>22099.568463</v>
       </c>
       <c r="F5" t="n">
-        <v>27420.404396</v>
+        <v>27644.293818</v>
       </c>
       <c r="G5" t="n">
-        <v>39944.594667</v>
+        <v>40409.018475</v>
       </c>
       <c r="H5" t="n">
-        <v>55215.911702</v>
+        <v>56142.815278</v>
       </c>
       <c r="I5" t="n">
-        <v>72830.318976</v>
+        <v>74835.44881099999</v>
       </c>
       <c r="J5" t="n">
         <v>147828.609446</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1151885.838634</v>
+        <v>1151833.24431</v>
       </c>
       <c r="F6" t="n">
-        <v>1192797.128131</v>
+        <v>1192645.39296</v>
       </c>
       <c r="G6" t="n">
-        <v>1249977.330692</v>
+        <v>1250100.094766</v>
       </c>
       <c r="H6" t="n">
-        <v>1323480.891089</v>
+        <v>1324538.166536</v>
       </c>
       <c r="I6" t="n">
-        <v>1415130.144925</v>
+        <v>1418524.120925</v>
       </c>
       <c r="J6" t="n">
         <v>1681748.46621</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>645036.447788</v>
+        <v>645095.371669</v>
       </c>
       <c r="F7" t="n">
-        <v>689646.061424</v>
+        <v>689719.143163</v>
       </c>
       <c r="G7" t="n">
-        <v>833796.680318</v>
+        <v>833611.974569</v>
       </c>
       <c r="H7" t="n">
-        <v>1005630.152536</v>
+        <v>1004620.315976</v>
       </c>
       <c r="I7" t="n">
-        <v>1174486.419634</v>
+        <v>1171022.500469</v>
       </c>
       <c r="J7" t="n">
         <v>1250313.030926</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>190400.809626</v>
+        <v>190590.766678</v>
       </c>
       <c r="F8" t="n">
-        <v>202337.705651</v>
+        <v>202789.553891</v>
       </c>
       <c r="G8" t="n">
-        <v>240857.055284</v>
+        <v>241767.464265</v>
       </c>
       <c r="H8" t="n">
-        <v>287756.484583</v>
+        <v>289560.911723</v>
       </c>
       <c r="I8" t="n">
-        <v>340628.567096</v>
+        <v>344539.430762</v>
       </c>
       <c r="J8" t="n">
         <v>515248.72342</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8429.172205999999</v>
+        <v>8512.541220999999</v>
       </c>
       <c r="F9" t="n">
-        <v>7237.605541</v>
+        <v>7406.473737</v>
       </c>
       <c r="G9" t="n">
-        <v>6944.748389</v>
+        <v>7241.355863</v>
       </c>
       <c r="H9" t="n">
-        <v>7391.733861</v>
+        <v>7907.300769</v>
       </c>
       <c r="I9" t="n">
-        <v>9524.955425</v>
+        <v>10516.491361</v>
       </c>
       <c r="J9" t="n">
         <v>36916.906542</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>120796.593855</v>
+        <v>120897.24663</v>
       </c>
       <c r="F10" t="n">
-        <v>113131.722426</v>
+        <v>113396.455452</v>
       </c>
       <c r="G10" t="n">
-        <v>113587.384459</v>
+        <v>114174.987686</v>
       </c>
       <c r="H10" t="n">
-        <v>120733.610462</v>
+        <v>121965.810302</v>
       </c>
       <c r="I10" t="n">
-        <v>134420.75787</v>
+        <v>137189.695501</v>
       </c>
       <c r="J10" t="n">
         <v>235545.819704</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388131.763215</v>
+        <v>389327.867454</v>
       </c>
       <c r="F11" t="n">
-        <v>394120.962159</v>
+        <v>396906.415729</v>
       </c>
       <c r="G11" t="n">
-        <v>445111.240322</v>
+        <v>450754.74497</v>
       </c>
       <c r="H11" t="n">
-        <v>520438.06212</v>
+        <v>531650.669444</v>
       </c>
       <c r="I11" t="n">
-        <v>633572.027846</v>
+        <v>657787.5356609999</v>
       </c>
       <c r="J11" t="n">
         <v>1439617.551623</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>482741.778472</v>
+        <v>481890.851607</v>
       </c>
       <c r="F12" t="n">
-        <v>503496.517343</v>
+        <v>501451.030583</v>
       </c>
       <c r="G12" t="n">
-        <v>586329.9444029999</v>
+        <v>581892.922912</v>
       </c>
       <c r="H12" t="n">
-        <v>679346.23194</v>
+        <v>669941.212036</v>
       </c>
       <c r="I12" t="n">
-        <v>726652.993314</v>
+        <v>705431.4148800001</v>
       </c>
       <c r="J12" t="n">
         <v>172453.438508</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>512867.69547</v>
+        <v>512983.903969</v>
       </c>
       <c r="F13" t="n">
-        <v>518049.99327</v>
+        <v>518432.014619</v>
       </c>
       <c r="G13" t="n">
-        <v>568371.20115</v>
+        <v>569376.160093</v>
       </c>
       <c r="H13" t="n">
-        <v>645719.78334</v>
+        <v>648104.5999499999</v>
       </c>
       <c r="I13" t="n">
-        <v>747038.991693</v>
+        <v>752871.260532</v>
       </c>
       <c r="J13" t="n">
         <v>1071295.38816</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1104.626519</v>
+        <v>1102.960977</v>
       </c>
       <c r="F14" t="n">
-        <v>1288.801253</v>
+        <v>1283.966965</v>
       </c>
       <c r="G14" t="n">
-        <v>2311.820994</v>
+        <v>2294.606262</v>
       </c>
       <c r="H14" t="n">
-        <v>3605.638788</v>
+        <v>3552.971105</v>
       </c>
       <c r="I14" t="n">
-        <v>5531.710398</v>
+        <v>5346.24069</v>
       </c>
       <c r="J14" t="n">
         <v>442969.332677</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>203613.956886</v>
+        <v>203614.93035</v>
       </c>
       <c r="F15" t="n">
-        <v>259419.937232</v>
+        <v>259422.505238</v>
       </c>
       <c r="G15" t="n">
-        <v>479026.000941</v>
+        <v>479034.493955</v>
       </c>
       <c r="H15" t="n">
-        <v>733641.033644</v>
+        <v>733666.250478</v>
       </c>
       <c r="I15" t="n">
-        <v>1013617.760397</v>
+        <v>1013706.524526</v>
       </c>
       <c r="J15" t="n">
         <v>1104070.59573</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25205.328492</v>
+        <v>25204.624723</v>
       </c>
       <c r="F16" t="n">
-        <v>25618.634527</v>
+        <v>25616.945205</v>
       </c>
       <c r="G16" t="n">
-        <v>38474.905178</v>
+        <v>38470.195059</v>
       </c>
       <c r="H16" t="n">
-        <v>51050.560503</v>
+        <v>51038.732556</v>
       </c>
       <c r="I16" t="n">
-        <v>64617.100378</v>
+        <v>64580.993103</v>
       </c>
       <c r="J16" t="n">
         <v>156752.635443</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73238.274108</v>
+        <v>73239.153198</v>
       </c>
       <c r="F17" t="n">
-        <v>84008.545489</v>
+        <v>84010.996765</v>
       </c>
       <c r="G17" t="n">
-        <v>142123.543408</v>
+        <v>142131.807512</v>
       </c>
       <c r="H17" t="n">
-        <v>202538.762745</v>
+        <v>202562.736853</v>
       </c>
       <c r="I17" t="n">
-        <v>262645.489013</v>
+        <v>262725.52817</v>
       </c>
       <c r="J17" t="n">
         <v>142284.443175</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>51162.055395</v>
+        <v>51162.572152</v>
       </c>
       <c r="F18" t="n">
-        <v>63632.267766</v>
+        <v>63633.772095</v>
       </c>
       <c r="G18" t="n">
-        <v>111225.159272</v>
+        <v>111230.327005</v>
       </c>
       <c r="H18" t="n">
-        <v>163078.005483</v>
+        <v>163093.310171</v>
       </c>
       <c r="I18" t="n">
-        <v>220979.269148</v>
+        <v>221032.042845</v>
       </c>
       <c r="J18" t="n">
         <v>166754.146294</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>226926.808587</v>
+        <v>227923.022617</v>
       </c>
       <c r="F19" t="n">
-        <v>242899.198241</v>
+        <v>245302.672856</v>
       </c>
       <c r="G19" t="n">
-        <v>263659.61199</v>
+        <v>268374.377148</v>
       </c>
       <c r="H19" t="n">
-        <v>292983.194623</v>
+        <v>301873.676471</v>
       </c>
       <c r="I19" t="n">
-        <v>345378.748433</v>
+        <v>362857.301453</v>
       </c>
       <c r="J19" t="n">
         <v>708309.355172</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21690.504646</v>
+        <v>21833.359878</v>
       </c>
       <c r="F20" t="n">
-        <v>22540.196909</v>
+        <v>22844.531835</v>
       </c>
       <c r="G20" t="n">
-        <v>24578.664236</v>
+        <v>25097.961412</v>
       </c>
       <c r="H20" t="n">
-        <v>26614.366578</v>
+        <v>27470.356049</v>
       </c>
       <c r="I20" t="n">
-        <v>29704.471863</v>
+        <v>31199.691203</v>
       </c>
       <c r="J20" t="n">
         <v>55555.788099</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>98372.68087900001</v>
+        <v>98111.107848</v>
       </c>
       <c r="F21" t="n">
-        <v>81380.77995700001</v>
+        <v>80920.70805299999</v>
       </c>
       <c r="G21" t="n">
-        <v>70506.38588099999</v>
+        <v>69824.242921</v>
       </c>
       <c r="H21" t="n">
-        <v>63950.956442</v>
+        <v>62923.700744</v>
       </c>
       <c r="I21" t="n">
-        <v>57440.602178</v>
+        <v>55752.74162</v>
       </c>
       <c r="J21" t="n">
         <v>27865.364813</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248636.02423</v>
+        <v>248990.682649</v>
       </c>
       <c r="F22" t="n">
-        <v>265485.62122</v>
+        <v>266263.924783</v>
       </c>
       <c r="G22" t="n">
-        <v>282188.200774</v>
+        <v>283626.700578</v>
       </c>
       <c r="H22" t="n">
-        <v>299498.335465</v>
+        <v>302194.468576</v>
       </c>
       <c r="I22" t="n">
-        <v>320077.478035</v>
+        <v>325468.156901</v>
       </c>
       <c r="J22" t="n">
         <v>439436.017604</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>752930.679752</v>
+        <v>750771.584469</v>
       </c>
       <c r="F23" t="n">
-        <v>842295.197647</v>
+        <v>836812.977399</v>
       </c>
       <c r="G23" t="n">
-        <v>950972.371909</v>
+        <v>939722.4934940001</v>
       </c>
       <c r="H23" t="n">
-        <v>1066550.593289</v>
+        <v>1044532.769087</v>
       </c>
       <c r="I23" t="n">
-        <v>1122049.015951</v>
+        <v>1077455.008937</v>
       </c>
       <c r="J23" t="n">
         <v>384439.63205</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11932.563876</v>
+        <v>12103.424792</v>
       </c>
       <c r="F24" t="n">
-        <v>12528.365727</v>
+        <v>12907.054952</v>
       </c>
       <c r="G24" t="n">
-        <v>13927.68399</v>
+        <v>14609.823403</v>
       </c>
       <c r="H24" t="n">
-        <v>16226.001361</v>
+        <v>17409.738402</v>
       </c>
       <c r="I24" t="n">
-        <v>21261.832646</v>
+        <v>23413.482315</v>
       </c>
       <c r="J24" t="n">
         <v>60970.683334</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23672.513223</v>
+        <v>23677.401727</v>
       </c>
       <c r="F25" t="n">
-        <v>21041.026008</v>
+        <v>21064.171974</v>
       </c>
       <c r="G25" t="n">
-        <v>19709.042062</v>
+        <v>19761.829131</v>
       </c>
       <c r="H25" t="n">
-        <v>19274.689792</v>
+        <v>19377.134364</v>
       </c>
       <c r="I25" t="n">
-        <v>19343.326896</v>
+        <v>19544.254517</v>
       </c>
       <c r="J25" t="n">
         <v>23139.340262</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>531350.0212589999</v>
+        <v>532235.83091</v>
       </c>
       <c r="F26" t="n">
-        <v>541610.811435</v>
+        <v>543876.646908</v>
       </c>
       <c r="G26" t="n">
-        <v>548606.4721660001</v>
+        <v>553369.838854</v>
       </c>
       <c r="H26" t="n">
-        <v>573355.194242</v>
+        <v>582872.79116</v>
       </c>
       <c r="I26" t="n">
-        <v>628939.672122</v>
+        <v>648583.084036</v>
       </c>
       <c r="J26" t="n">
         <v>1058081.078469</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>287186.623793</v>
+        <v>287082.192792</v>
       </c>
       <c r="F27" t="n">
-        <v>297590.071095</v>
+        <v>297427.331027</v>
       </c>
       <c r="G27" t="n">
-        <v>302008.138094</v>
+        <v>301963.342742</v>
       </c>
       <c r="H27" t="n">
-        <v>311590.867257</v>
+        <v>311990.870209</v>
       </c>
       <c r="I27" t="n">
-        <v>327044.470282</v>
+        <v>328628.314437</v>
       </c>
       <c r="J27" t="n">
         <v>390636.118207</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95763.25795699999</v>
+        <v>95733.070519</v>
       </c>
       <c r="F28" t="n">
-        <v>89026.448917</v>
+        <v>88977.697367</v>
       </c>
       <c r="G28" t="n">
-        <v>96099.788053</v>
+        <v>95905.749469</v>
       </c>
       <c r="H28" t="n">
-        <v>108213.483176</v>
+        <v>107612.177161</v>
       </c>
       <c r="I28" t="n">
-        <v>119961.462655</v>
+        <v>118299.045641</v>
       </c>
       <c r="J28" t="n">
         <v>94798.959088</v>
@@ -2578,58 +2578,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>142418.113357</v>
+        <v>142508.720103</v>
       </c>
       <c r="F29" t="n">
-        <v>127795.031789</v>
+        <v>128044.357911</v>
       </c>
       <c r="G29" t="n">
-        <v>120870.683047</v>
+        <v>121337.905503</v>
       </c>
       <c r="H29" t="n">
-        <v>117503.895493</v>
+        <v>118214.21649</v>
       </c>
       <c r="I29" t="n">
-        <v>120254.446755</v>
+        <v>121233.244489</v>
       </c>
       <c r="J29" t="n">
-        <v>127087.920211</v>
+        <v>128355.345928</v>
       </c>
       <c r="K29" t="n">
-        <v>138248.727766</v>
+        <v>139839.019729</v>
       </c>
       <c r="L29" t="n">
-        <v>153263.184634</v>
+        <v>155215.676283</v>
       </c>
       <c r="M29" t="n">
-        <v>168258.202941</v>
+        <v>170585.345209</v>
       </c>
       <c r="N29" t="n">
-        <v>184755.531647</v>
+        <v>187497.669755</v>
       </c>
       <c r="O29" t="n">
-        <v>204356.780923</v>
+        <v>207592.264989</v>
       </c>
       <c r="P29" t="n">
-        <v>226984.397806</v>
+        <v>230809.247465</v>
       </c>
       <c r="Q29" t="n">
-        <v>252179.078674</v>
+        <v>256705.416985</v>
       </c>
       <c r="R29" t="n">
-        <v>279192.787014</v>
+        <v>284543.099552</v>
       </c>
       <c r="S29" t="n">
-        <v>307557.807096</v>
+        <v>313850.744737</v>
       </c>
       <c r="T29" t="n">
-        <v>336888.305788</v>
+        <v>344276.699541</v>
       </c>
       <c r="U29" t="n">
-        <v>367831.2999</v>
+        <v>376488.987752</v>
       </c>
       <c r="V29" t="n">
-        <v>403712.125373</v>
+        <v>413919.602999</v>
       </c>
     </row>
     <row r="30">
@@ -2654,58 +2654,58 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>237520.753726</v>
+        <v>237717.888672</v>
       </c>
       <c r="F30" t="n">
-        <v>173865.172135</v>
+        <v>174526.583352</v>
       </c>
       <c r="G30" t="n">
-        <v>135502.241177</v>
+        <v>136728.097776</v>
       </c>
       <c r="H30" t="n">
-        <v>119296.369474</v>
+        <v>121069.984616</v>
       </c>
       <c r="I30" t="n">
-        <v>118900.23751</v>
+        <v>121280.121738</v>
       </c>
       <c r="J30" t="n">
-        <v>128042.060634</v>
+        <v>131120.979628</v>
       </c>
       <c r="K30" t="n">
-        <v>144788.49149</v>
+        <v>148714.504181</v>
       </c>
       <c r="L30" t="n">
-        <v>167991.116709</v>
+        <v>172945.557459</v>
       </c>
       <c r="M30" t="n">
-        <v>193344.28181</v>
+        <v>199424.734269</v>
       </c>
       <c r="N30" t="n">
-        <v>222401.929138</v>
+        <v>229773.549581</v>
       </c>
       <c r="O30" t="n">
-        <v>257571.844606</v>
+        <v>266515.827232</v>
       </c>
       <c r="P30" t="n">
-        <v>299629.900519</v>
+        <v>310498.505801</v>
       </c>
       <c r="Q30" t="n">
-        <v>349159.940381</v>
+        <v>362356.417052</v>
       </c>
       <c r="R30" t="n">
-        <v>406022.621328</v>
+        <v>421995.621768</v>
       </c>
       <c r="S30" t="n">
-        <v>470723.187206</v>
+        <v>489989.409559</v>
       </c>
       <c r="T30" t="n">
-        <v>542849.766982</v>
+        <v>565985.040393</v>
       </c>
       <c r="U30" t="n">
-        <v>625094.176449</v>
+        <v>652849.656159</v>
       </c>
       <c r="V30" t="n">
-        <v>724719.962141</v>
+        <v>758182.735659</v>
       </c>
     </row>
     <row r="31">
@@ -2730,58 +2730,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>402989.054804</v>
+        <v>401971.689811</v>
       </c>
       <c r="F31" t="n">
-        <v>343245.187647</v>
+        <v>341756.989031</v>
       </c>
       <c r="G31" t="n">
-        <v>295555.729482</v>
+        <v>293994.268844</v>
       </c>
       <c r="H31" t="n">
-        <v>267297.237305</v>
+        <v>265741.240051</v>
       </c>
       <c r="I31" t="n">
-        <v>257955.553681</v>
+        <v>256328.580593</v>
       </c>
       <c r="J31" t="n">
-        <v>259696.943214</v>
+        <v>257891.913182</v>
       </c>
       <c r="K31" t="n">
-        <v>270187.37414</v>
+        <v>268082.116382</v>
       </c>
       <c r="L31" t="n">
-        <v>287206.733302</v>
+        <v>284670.31389</v>
       </c>
       <c r="M31" t="n">
-        <v>304278.800132</v>
+        <v>301231.243684</v>
       </c>
       <c r="N31" t="n">
-        <v>325449.065062</v>
+        <v>321753.519158</v>
       </c>
       <c r="O31" t="n">
-        <v>353019.164143</v>
+        <v>348479.910536</v>
       </c>
       <c r="P31" t="n">
-        <v>385654.431661</v>
+        <v>380048.889682</v>
       </c>
       <c r="Q31" t="n">
-        <v>421591.745732</v>
+        <v>414664.516529</v>
       </c>
       <c r="R31" t="n">
-        <v>457908.355505</v>
+        <v>449387.205481</v>
       </c>
       <c r="S31" t="n">
-        <v>493102.863873</v>
+        <v>482663.761283</v>
       </c>
       <c r="T31" t="n">
-        <v>524515.418546</v>
+        <v>511794.664715</v>
       </c>
       <c r="U31" t="n">
-        <v>551308.591697</v>
+        <v>535810.802668</v>
       </c>
       <c r="V31" t="n">
-        <v>574054.15714</v>
+        <v>555043.25048</v>
       </c>
     </row>
     <row r="32">
@@ -2806,58 +2806,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>365098.534214</v>
+        <v>365127.256554</v>
       </c>
       <c r="F32" t="n">
-        <v>289617.104617</v>
+        <v>289992.407845</v>
       </c>
       <c r="G32" t="n">
-        <v>242164.953831</v>
+        <v>243049.529349</v>
       </c>
       <c r="H32" t="n">
-        <v>217029.987077</v>
+        <v>218408.737221</v>
       </c>
       <c r="I32" t="n">
-        <v>212010.656255</v>
+        <v>213876.238377</v>
       </c>
       <c r="J32" t="n">
-        <v>218926.892593</v>
+        <v>221284.27192</v>
       </c>
       <c r="K32" t="n">
-        <v>235561.397071</v>
+        <v>238448.626121</v>
       </c>
       <c r="L32" t="n">
-        <v>259573.334082</v>
+        <v>263044.798463</v>
       </c>
       <c r="M32" t="n">
-        <v>284649.075941</v>
+        <v>288692.605667</v>
       </c>
       <c r="N32" t="n">
-        <v>313364.633748</v>
+        <v>318013.051757</v>
       </c>
       <c r="O32" t="n">
-        <v>348603.725759</v>
+        <v>353966.601366</v>
       </c>
       <c r="P32" t="n">
-        <v>389929.664799</v>
+        <v>396141.312759</v>
       </c>
       <c r="Q32" t="n">
-        <v>436989.799433</v>
+        <v>444210.550769</v>
       </c>
       <c r="R32" t="n">
-        <v>488451.205112</v>
+        <v>496864.8469</v>
       </c>
       <c r="S32" t="n">
-        <v>543831.260735</v>
+        <v>553628.861862</v>
       </c>
       <c r="T32" t="n">
-        <v>602091.564606</v>
+        <v>613487.559904</v>
       </c>
       <c r="U32" t="n">
-        <v>664629.325569</v>
+        <v>677895.884982</v>
       </c>
       <c r="V32" t="n">
-        <v>736991.465597</v>
+        <v>752557.967861</v>
       </c>
     </row>
     <row r="33">
@@ -2882,58 +2882,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>379579.520286</v>
+        <v>379659.762671</v>
       </c>
       <c r="F33" t="n">
-        <v>327570.145198</v>
+        <v>327945.104263</v>
       </c>
       <c r="G33" t="n">
-        <v>296157.256419</v>
+        <v>296983.494816</v>
       </c>
       <c r="H33" t="n">
-        <v>277722.092908</v>
+        <v>279030.64046</v>
       </c>
       <c r="I33" t="n">
-        <v>275744.598259</v>
+        <v>277553.331763</v>
       </c>
       <c r="J33" t="n">
-        <v>282822.428949</v>
+        <v>285147.085992</v>
       </c>
       <c r="K33" t="n">
-        <v>297826.532289</v>
+        <v>300708.893929</v>
       </c>
       <c r="L33" t="n">
-        <v>319135.780889</v>
+        <v>322636.333496</v>
       </c>
       <c r="M33" t="n">
-        <v>339703.613338</v>
+        <v>343820.793845</v>
       </c>
       <c r="N33" t="n">
-        <v>363362.763431</v>
+        <v>368145.409933</v>
       </c>
       <c r="O33" t="n">
-        <v>393045.504902</v>
+        <v>398606.5829</v>
       </c>
       <c r="P33" t="n">
-        <v>428351.838376</v>
+        <v>434857.293119</v>
       </c>
       <c r="Q33" t="n">
-        <v>467887.070662</v>
+        <v>475507.833707</v>
       </c>
       <c r="R33" t="n">
-        <v>510212.799628</v>
+        <v>519149.224139</v>
       </c>
       <c r="S33" t="n">
-        <v>555055.598323</v>
+        <v>565522.991147</v>
       </c>
       <c r="T33" t="n">
-        <v>601477.253933</v>
+        <v>613715.822609</v>
       </c>
       <c r="U33" t="n">
-        <v>651300.5006030001</v>
+        <v>665635.200573</v>
       </c>
       <c r="V33" t="n">
-        <v>709304.378099</v>
+        <v>726193.064779</v>
       </c>
     </row>
     <row r="34">
@@ -2958,58 +2958,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1598223.569038</v>
+        <v>1596535.451535</v>
       </c>
       <c r="F34" t="n">
-        <v>2402857.19802</v>
+        <v>2396191.958091</v>
       </c>
       <c r="G34" t="n">
-        <v>3627708.403593</v>
+        <v>3612131.605437</v>
       </c>
       <c r="H34" t="n">
-        <v>4834148.20073</v>
+        <v>4808086.754385</v>
       </c>
       <c r="I34" t="n">
-        <v>5989603.100922</v>
+        <v>5951701.042564</v>
       </c>
       <c r="J34" t="n">
-        <v>7002423.234343</v>
+        <v>6951307.219123</v>
       </c>
       <c r="K34" t="n">
-        <v>7941029.256145</v>
+        <v>7874518.378489</v>
       </c>
       <c r="L34" t="n">
-        <v>8841008.167729</v>
+        <v>8756358.699883999</v>
       </c>
       <c r="M34" t="n">
-        <v>9590040.969571</v>
+        <v>9485857.833784999</v>
       </c>
       <c r="N34" t="n">
-        <v>10345172.292059</v>
+        <v>10218359.66969</v>
       </c>
       <c r="O34" t="n">
-        <v>11228439.959873</v>
+        <v>11073706.605003</v>
       </c>
       <c r="P34" t="n">
-        <v>12226069.120333</v>
+        <v>12037099.56658</v>
       </c>
       <c r="Q34" t="n">
-        <v>13304652.349383</v>
+        <v>13073880.084174</v>
       </c>
       <c r="R34" t="n">
-        <v>14379869.442868</v>
+        <v>14099294.540321</v>
       </c>
       <c r="S34" t="n">
-        <v>15408030.479109</v>
+        <v>15067934.970459</v>
       </c>
       <c r="T34" t="n">
-        <v>16309066.884841</v>
+        <v>15898758.023327</v>
       </c>
       <c r="U34" t="n">
-        <v>17053485.975831</v>
+        <v>16558516.321702</v>
       </c>
       <c r="V34" t="n">
-        <v>17652731.515689</v>
+        <v>17051718.964391</v>
       </c>
     </row>
     <row r="35">
@@ -3034,58 +3034,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>92154.846706</v>
+        <v>92151.89934600001</v>
       </c>
       <c r="F35" t="n">
-        <v>98590.898489</v>
+        <v>98567.739501</v>
       </c>
       <c r="G35" t="n">
-        <v>107973.999873</v>
+        <v>107945.897731</v>
       </c>
       <c r="H35" t="n">
-        <v>113185.788756</v>
+        <v>113193.765238</v>
       </c>
       <c r="I35" t="n">
-        <v>117656.46402</v>
+        <v>117730.830937</v>
       </c>
       <c r="J35" t="n">
-        <v>121396.923578</v>
+        <v>121555.046812</v>
       </c>
       <c r="K35" t="n">
-        <v>126578.064382</v>
+        <v>126828.628027</v>
       </c>
       <c r="L35" t="n">
-        <v>133715.082699</v>
+        <v>134063.962607</v>
       </c>
       <c r="M35" t="n">
-        <v>140361.232314</v>
+        <v>140811.516334</v>
       </c>
       <c r="N35" t="n">
-        <v>148368.009926</v>
+        <v>148926.435283</v>
       </c>
       <c r="O35" t="n">
-        <v>158662.207092</v>
+        <v>159344.670781</v>
       </c>
       <c r="P35" t="n">
-        <v>170789.366032</v>
+        <v>171627.569549</v>
       </c>
       <c r="Q35" t="n">
-        <v>183960.089076</v>
+        <v>184991.835183</v>
       </c>
       <c r="R35" t="n">
-        <v>197497.759207</v>
+        <v>198770.175872</v>
       </c>
       <c r="S35" t="n">
-        <v>211068.220017</v>
+        <v>212630.671103</v>
       </c>
       <c r="T35" t="n">
-        <v>224097.472049</v>
+        <v>226008.716688</v>
       </c>
       <c r="U35" t="n">
-        <v>236877.699071</v>
+        <v>239211.017224</v>
       </c>
       <c r="V35" t="n">
-        <v>251109.894246</v>
+        <v>253976.390838</v>
       </c>
     </row>
     <row r="36">
@@ -3110,58 +3110,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42771.942413</v>
+        <v>42675.358274</v>
       </c>
       <c r="F36" t="n">
-        <v>37025.85781</v>
+        <v>36881.134918</v>
       </c>
       <c r="G36" t="n">
-        <v>29691.010615</v>
+        <v>29553.632088</v>
       </c>
       <c r="H36" t="n">
-        <v>23757.910222</v>
+        <v>23643.68562</v>
       </c>
       <c r="I36" t="n">
-        <v>20171.110122</v>
+        <v>20073.568729</v>
       </c>
       <c r="J36" t="n">
-        <v>18109.885383</v>
+        <v>18019.525184</v>
       </c>
       <c r="K36" t="n">
-        <v>16987.611297</v>
+        <v>16897.013548</v>
       </c>
       <c r="L36" t="n">
-        <v>16381.596332</v>
+        <v>16285.511192</v>
       </c>
       <c r="M36" t="n">
-        <v>15675.776806</v>
+        <v>15574.448548</v>
       </c>
       <c r="N36" t="n">
-        <v>15004.757417</v>
+        <v>14898.440405</v>
       </c>
       <c r="O36" t="n">
-        <v>14527.760523</v>
+        <v>14415.542305</v>
       </c>
       <c r="P36" t="n">
-        <v>14222.018669</v>
+        <v>14102.307013</v>
       </c>
       <c r="Q36" t="n">
-        <v>14021.440381</v>
+        <v>13892.311085</v>
       </c>
       <c r="R36" t="n">
-        <v>13814.021421</v>
+        <v>13674.396309</v>
       </c>
       <c r="S36" t="n">
-        <v>13550.834398</v>
+        <v>13400.020107</v>
       </c>
       <c r="T36" t="n">
-        <v>13196.791836</v>
+        <v>13034.657992</v>
       </c>
       <c r="U36" t="n">
-        <v>12792.492348</v>
+        <v>12617.676736</v>
       </c>
       <c r="V36" t="n">
-        <v>12394.408293</v>
+        <v>12204.439056</v>
       </c>
     </row>
     <row r="37">
@@ -3186,58 +3186,58 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221593.375858</v>
+        <v>221039.89586</v>
       </c>
       <c r="F37" t="n">
-        <v>167155.16056</v>
+        <v>166457.619168</v>
       </c>
       <c r="G37" t="n">
-        <v>131758.680703</v>
+        <v>131111.651965</v>
       </c>
       <c r="H37" t="n">
-        <v>110307.97501</v>
+        <v>109737.287258</v>
       </c>
       <c r="I37" t="n">
-        <v>100126.580543</v>
+        <v>99590.348564</v>
       </c>
       <c r="J37" t="n">
-        <v>95563.70939600001</v>
+        <v>95022.96030599999</v>
       </c>
       <c r="K37" t="n">
-        <v>94681.017545</v>
+        <v>94101.73226800001</v>
       </c>
       <c r="L37" t="n">
-        <v>95827.822296</v>
+        <v>95184.75877</v>
       </c>
       <c r="M37" t="n">
-        <v>96569.026549</v>
+        <v>95856.841799</v>
       </c>
       <c r="N37" t="n">
-        <v>98162.939375</v>
+        <v>97366.65240000001</v>
       </c>
       <c r="O37" t="n">
-        <v>101563.346065</v>
+        <v>100655.253954</v>
       </c>
       <c r="P37" t="n">
-        <v>106384.570705</v>
+        <v>105334.414688</v>
       </c>
       <c r="Q37" t="n">
-        <v>111928.904197</v>
+        <v>110706.423277</v>
       </c>
       <c r="R37" t="n">
-        <v>117550.971483</v>
+        <v>116129.578194</v>
       </c>
       <c r="S37" t="n">
-        <v>122745.80053</v>
+        <v>121096.048493</v>
       </c>
       <c r="T37" t="n">
-        <v>127162.994868</v>
+        <v>125256.007439</v>
       </c>
       <c r="U37" t="n">
-        <v>130717.455674</v>
+        <v>128509.294447</v>
       </c>
       <c r="V37" t="n">
-        <v>133946.336327</v>
+        <v>131369.048782</v>
       </c>
     </row>
     <row r="38">
@@ -3262,58 +3262,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>239588.946932</v>
+        <v>240338.952856</v>
       </c>
       <c r="F38" t="n">
-        <v>218864.809193</v>
+        <v>220293.03705</v>
       </c>
       <c r="G38" t="n">
-        <v>200194.10023</v>
+        <v>202358.713657</v>
       </c>
       <c r="H38" t="n">
-        <v>190424.784198</v>
+        <v>193336.705857</v>
       </c>
       <c r="I38" t="n">
-        <v>194369.671373</v>
+        <v>198129.160799</v>
       </c>
       <c r="J38" t="n">
-        <v>208274.14337</v>
+        <v>213002.366882</v>
       </c>
       <c r="K38" t="n">
-        <v>231245.419926</v>
+        <v>237132.394148</v>
       </c>
       <c r="L38" t="n">
-        <v>261947.812941</v>
+        <v>269220.668034</v>
       </c>
       <c r="M38" t="n">
-        <v>293834.26583</v>
+        <v>302595.37317</v>
       </c>
       <c r="N38" t="n">
-        <v>329789.600367</v>
+        <v>340249.277934</v>
       </c>
       <c r="O38" t="n">
-        <v>373577.001971</v>
+        <v>386104.499247</v>
       </c>
       <c r="P38" t="n">
-        <v>426238.19541</v>
+        <v>441294.840017</v>
       </c>
       <c r="Q38" t="n">
-        <v>488233.17045</v>
+        <v>506332.170231</v>
       </c>
       <c r="R38" t="n">
-        <v>559216.861391</v>
+        <v>580945.827038</v>
       </c>
       <c r="S38" t="n">
-        <v>639199.025406</v>
+        <v>665203.608276</v>
       </c>
       <c r="T38" t="n">
-        <v>727174.293407</v>
+        <v>758190.75126</v>
       </c>
       <c r="U38" t="n">
-        <v>825928.536393</v>
+        <v>862910.017522</v>
       </c>
       <c r="V38" t="n">
-        <v>945111.144117</v>
+        <v>989519.477852</v>
       </c>
     </row>
     <row r="39">
@@ -3338,58 +3338,58 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>915540.4059369999</v>
+        <v>913246.272611</v>
       </c>
       <c r="F39" t="n">
-        <v>718747.27482</v>
+        <v>715712.2154099999</v>
       </c>
       <c r="G39" t="n">
-        <v>603466.300212</v>
+        <v>600400.886407</v>
       </c>
       <c r="H39" t="n">
-        <v>540060.764341</v>
+        <v>537072.4248170001</v>
       </c>
       <c r="I39" t="n">
-        <v>521629.959928</v>
+        <v>518520.478988</v>
       </c>
       <c r="J39" t="n">
-        <v>526637.611726</v>
+        <v>523180.386415</v>
       </c>
       <c r="K39" t="n">
-        <v>547848.369312</v>
+        <v>543810.30013</v>
       </c>
       <c r="L39" t="n">
-        <v>579514.146441</v>
+        <v>574667.072456</v>
       </c>
       <c r="M39" t="n">
-        <v>606860.2774660001</v>
+        <v>601109.4527</v>
       </c>
       <c r="N39" t="n">
-        <v>636700.704058</v>
+        <v>629888.800059</v>
       </c>
       <c r="O39" t="n">
-        <v>676111.777547</v>
+        <v>667972.8644439999</v>
       </c>
       <c r="P39" t="n">
-        <v>725449.283904</v>
+        <v>715640.291878</v>
       </c>
       <c r="Q39" t="n">
-        <v>783574.929926</v>
+        <v>771651.644291</v>
       </c>
       <c r="R39" t="n">
-        <v>846629.083688</v>
+        <v>832080.722485</v>
       </c>
       <c r="S39" t="n">
-        <v>911680.850542</v>
+        <v>893881.190057</v>
       </c>
       <c r="T39" t="n">
-        <v>973128.110964</v>
+        <v>951389.852607</v>
       </c>
       <c r="U39" t="n">
-        <v>1028823.971295</v>
+        <v>1002234.752335</v>
       </c>
       <c r="V39" t="n">
-        <v>1079919.407838</v>
+        <v>1047149.717987</v>
       </c>
     </row>
     <row r="40">
@@ -3414,58 +3414,58 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>139559.097528</v>
+        <v>139213.018364</v>
       </c>
       <c r="F40" t="n">
-        <v>120048.22636</v>
+        <v>119537.158366</v>
       </c>
       <c r="G40" t="n">
-        <v>106206.258058</v>
+        <v>105653.03146</v>
       </c>
       <c r="H40" t="n">
-        <v>95860.37216299999</v>
+        <v>95311.768639</v>
       </c>
       <c r="I40" t="n">
-        <v>92180.505168</v>
+        <v>91610.77792199999</v>
       </c>
       <c r="J40" t="n">
-        <v>91595.826974</v>
+        <v>90975.85868400001</v>
       </c>
       <c r="K40" t="n">
-        <v>94223.793256</v>
+        <v>93512.04226</v>
       </c>
       <c r="L40" t="n">
-        <v>99132.800126</v>
+        <v>98286.43657000001</v>
       </c>
       <c r="M40" t="n">
-        <v>104218.808322</v>
+        <v>103210.890552</v>
       </c>
       <c r="N40" t="n">
-        <v>110258.77753</v>
+        <v>109051.972604</v>
       </c>
       <c r="O40" t="n">
-        <v>118165.855981</v>
+        <v>116705.171161</v>
       </c>
       <c r="P40" t="n">
-        <v>127466.33211</v>
+        <v>125689.372599</v>
       </c>
       <c r="Q40" t="n">
-        <v>137797.461926</v>
+        <v>135630.622412</v>
       </c>
       <c r="R40" t="n">
-        <v>148311.729339</v>
+        <v>145674.661064</v>
       </c>
       <c r="S40" t="n">
-        <v>158490.676727</v>
+        <v>155286.235032</v>
       </c>
       <c r="T40" t="n">
-        <v>167663.597253</v>
+        <v>163783.0842</v>
       </c>
       <c r="U40" t="n">
-        <v>175376.534702</v>
+        <v>170674.444056</v>
       </c>
       <c r="V40" t="n">
-        <v>182041.256535</v>
+        <v>176299.415053</v>
       </c>
     </row>
     <row r="41">
@@ -3490,58 +3490,58 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>164361.847839</v>
+        <v>163967.869553</v>
       </c>
       <c r="F41" t="n">
-        <v>158087.232141</v>
+        <v>157426.129551</v>
       </c>
       <c r="G41" t="n">
-        <v>145788.043779</v>
+        <v>145041.439558</v>
       </c>
       <c r="H41" t="n">
-        <v>135301.726286</v>
+        <v>134541.975988</v>
       </c>
       <c r="I41" t="n">
-        <v>131678.749566</v>
+        <v>130885.509874</v>
       </c>
       <c r="J41" t="n">
-        <v>132384.334702</v>
+        <v>131516.441792</v>
       </c>
       <c r="K41" t="n">
-        <v>136733.491434</v>
+        <v>135741.548787</v>
       </c>
       <c r="L41" t="n">
-        <v>143529.924957</v>
+        <v>142365.190505</v>
       </c>
       <c r="M41" t="n">
-        <v>149614.270968</v>
+        <v>148256.453771</v>
       </c>
       <c r="N41" t="n">
-        <v>156625.317049</v>
+        <v>155038.926375</v>
       </c>
       <c r="O41" t="n">
-        <v>165723.542438</v>
+        <v>163855.515455</v>
       </c>
       <c r="P41" t="n">
-        <v>176564.526883</v>
+        <v>174355.631536</v>
       </c>
       <c r="Q41" t="n">
-        <v>188552.01014</v>
+        <v>185932.662802</v>
       </c>
       <c r="R41" t="n">
-        <v>200773.193473</v>
+        <v>197669.990683</v>
       </c>
       <c r="S41" t="n">
-        <v>212721.646584</v>
+        <v>209043.642546</v>
       </c>
       <c r="T41" t="n">
-        <v>223409.202785</v>
+        <v>219060.170512</v>
       </c>
       <c r="U41" t="n">
-        <v>232575.753341</v>
+        <v>227426.590269</v>
       </c>
       <c r="V41" t="n">
-        <v>240479.512477</v>
+        <v>234341.249635</v>
       </c>
     </row>
     <row r="42">
@@ -3566,58 +3566,58 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8893.610103999999</v>
+        <v>8942.408974</v>
       </c>
       <c r="F42" t="n">
-        <v>7713.443632</v>
+        <v>7805.594843</v>
       </c>
       <c r="G42" t="n">
-        <v>6964.223312</v>
+        <v>7098.299004</v>
       </c>
       <c r="H42" t="n">
-        <v>6509.768135</v>
+        <v>6684.391121</v>
       </c>
       <c r="I42" t="n">
-        <v>6466.5914</v>
+        <v>6686.653165</v>
       </c>
       <c r="J42" t="n">
-        <v>6695.976317</v>
+        <v>6968.164152</v>
       </c>
       <c r="K42" t="n">
-        <v>7128.701887</v>
+        <v>7463.4904</v>
       </c>
       <c r="L42" t="n">
-        <v>7747.234581</v>
+        <v>8157.784895</v>
       </c>
       <c r="M42" t="n">
-        <v>8324.056662000001</v>
+        <v>8815.119500999999</v>
       </c>
       <c r="N42" t="n">
-        <v>8974.024551</v>
+        <v>9556.878403000001</v>
       </c>
       <c r="O42" t="n">
-        <v>9809.185267999999</v>
+        <v>10503.282559</v>
       </c>
       <c r="P42" t="n">
-        <v>10823.673582</v>
+        <v>11650.481276</v>
       </c>
       <c r="Q42" t="n">
-        <v>12028.257913</v>
+        <v>13014.759151</v>
       </c>
       <c r="R42" t="n">
-        <v>13405.653654</v>
+        <v>14579.218782</v>
       </c>
       <c r="S42" t="n">
-        <v>14993.195734</v>
+        <v>16384.940049</v>
       </c>
       <c r="T42" t="n">
-        <v>16822.683766</v>
+        <v>18465.687569</v>
       </c>
       <c r="U42" t="n">
-        <v>19040.166225</v>
+        <v>20976.099772</v>
       </c>
       <c r="V42" t="n">
-        <v>22009.094794</v>
+        <v>24301.430728</v>
       </c>
     </row>
     <row r="43">
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>406144.120494</v>
+        <v>405101.310906</v>
       </c>
       <c r="F43" t="n">
-        <v>470775.545286</v>
+        <v>468611.574305</v>
       </c>
       <c r="G43" t="n">
-        <v>538387.797424</v>
+        <v>535212.3396900001</v>
       </c>
       <c r="H43" t="n">
-        <v>602105.8937360001</v>
+        <v>597996.609439</v>
       </c>
       <c r="I43" t="n">
-        <v>678925.791946</v>
+        <v>673700.475275</v>
       </c>
       <c r="J43" t="n">
-        <v>766842.7093850001</v>
+        <v>760162.931156</v>
       </c>
       <c r="K43" t="n">
-        <v>871286.750982</v>
+        <v>862651.582897</v>
       </c>
       <c r="L43" t="n">
-        <v>993225.752397</v>
+        <v>982001.722261</v>
       </c>
       <c r="M43" t="n">
-        <v>1111844.356548</v>
+        <v>1097592.497329</v>
       </c>
       <c r="N43" t="n">
-        <v>1239059.737627</v>
+        <v>1221139.6634</v>
       </c>
       <c r="O43" t="n">
-        <v>1386929.242773</v>
+        <v>1364378.707872</v>
       </c>
       <c r="P43" t="n">
-        <v>1554307.452998</v>
+        <v>1525949.13824</v>
       </c>
       <c r="Q43" t="n">
-        <v>1738139.210219</v>
+        <v>1702518.503421</v>
       </c>
       <c r="R43" t="n">
-        <v>1929824.520032</v>
+        <v>1885256.033792</v>
       </c>
       <c r="S43" t="n">
-        <v>2119821.891717</v>
+        <v>2064290.546897</v>
       </c>
       <c r="T43" t="n">
-        <v>2290405.841981</v>
+        <v>2221774.619986</v>
       </c>
       <c r="U43" t="n">
-        <v>2430972.007545</v>
+        <v>2346553.386163</v>
       </c>
       <c r="V43" t="n">
-        <v>2537620.651699</v>
+        <v>2433599.167951</v>
       </c>
     </row>
     <row r="44">
@@ -3718,58 +3718,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>187692.883829</v>
+        <v>188041.09761</v>
       </c>
       <c r="F44" t="n">
-        <v>177410.590016</v>
+        <v>178135.477305</v>
       </c>
       <c r="G44" t="n">
-        <v>172311.787408</v>
+        <v>173495.221279</v>
       </c>
       <c r="H44" t="n">
-        <v>173252.011856</v>
+        <v>174935.649345</v>
       </c>
       <c r="I44" t="n">
-        <v>183474.894482</v>
+        <v>185735.713527</v>
       </c>
       <c r="J44" t="n">
-        <v>199653.870764</v>
+        <v>202567.766447</v>
       </c>
       <c r="K44" t="n">
-        <v>221313.748093</v>
+        <v>224997.835168</v>
       </c>
       <c r="L44" t="n">
-        <v>247523.337957</v>
+        <v>252112.89294</v>
       </c>
       <c r="M44" t="n">
-        <v>272365.579124</v>
+        <v>277921.854216</v>
       </c>
       <c r="N44" t="n">
-        <v>298772.233349</v>
+        <v>305428.008466</v>
       </c>
       <c r="O44" t="n">
-        <v>330120.797022</v>
+        <v>338112.871009</v>
       </c>
       <c r="P44" t="n">
-        <v>366688.850704</v>
+        <v>376294.706978</v>
       </c>
       <c r="Q44" t="n">
-        <v>408784.41428</v>
+        <v>420340.503061</v>
       </c>
       <c r="R44" t="n">
-        <v>455353.167466</v>
+        <v>469206.365318</v>
       </c>
       <c r="S44" t="n">
-        <v>506378.046987</v>
+        <v>522930.119801</v>
       </c>
       <c r="T44" t="n">
-        <v>560791.349502</v>
+        <v>580494.550484</v>
       </c>
       <c r="U44" t="n">
-        <v>620492.002815</v>
+        <v>643921.848532</v>
       </c>
       <c r="V44" t="n">
-        <v>692076.078062</v>
+        <v>720121.489876</v>
       </c>
     </row>
     <row r="45">
@@ -3794,58 +3794,58 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>38109.541725</v>
+        <v>38214.126813</v>
       </c>
       <c r="F45" t="n">
-        <v>36391.89174</v>
+        <v>36587.376062</v>
       </c>
       <c r="G45" t="n">
-        <v>34669.909498</v>
+        <v>34965.956253</v>
       </c>
       <c r="H45" t="n">
-        <v>33299.821823</v>
+        <v>33700.702222</v>
       </c>
       <c r="I45" t="n">
-        <v>33559.954449</v>
+        <v>34077.948877</v>
       </c>
       <c r="J45" t="n">
-        <v>35035.753903</v>
+        <v>35683.509066</v>
       </c>
       <c r="K45" t="n">
-        <v>37815.444836</v>
+        <v>38612.615198</v>
       </c>
       <c r="L45" t="n">
-        <v>41743.017192</v>
+        <v>42714.739381</v>
       </c>
       <c r="M45" t="n">
-        <v>45945.425155</v>
+        <v>47101.075887</v>
       </c>
       <c r="N45" t="n">
-        <v>50343.270545</v>
+        <v>51710.250385</v>
       </c>
       <c r="O45" t="n">
-        <v>55500.717341</v>
+        <v>57125.452332</v>
       </c>
       <c r="P45" t="n">
-        <v>61599.42136</v>
+        <v>63537.6966</v>
       </c>
       <c r="Q45" t="n">
-        <v>68963.13291099999</v>
+        <v>71281.484033</v>
       </c>
       <c r="R45" t="n">
-        <v>77481.408662</v>
+        <v>80248.782777</v>
       </c>
       <c r="S45" t="n">
-        <v>87193.807321</v>
+        <v>90493.476056</v>
       </c>
       <c r="T45" t="n">
-        <v>97960.399516</v>
+        <v>101890.00587</v>
       </c>
       <c r="U45" t="n">
-        <v>110135.953121</v>
+        <v>114820.373982</v>
       </c>
       <c r="V45" t="n">
-        <v>125007.780786</v>
+        <v>130642.730365</v>
       </c>
     </row>
     <row r="46">
@@ -3870,58 +3870,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>128880.379154</v>
+        <v>129318.123089</v>
       </c>
       <c r="F46" t="n">
-        <v>120819.000223</v>
+        <v>121725.876569</v>
       </c>
       <c r="G46" t="n">
-        <v>120640.843144</v>
+        <v>122101.976031</v>
       </c>
       <c r="H46" t="n">
-        <v>127573.561523</v>
+        <v>129674.375039</v>
       </c>
       <c r="I46" t="n">
-        <v>148891.129894</v>
+        <v>151797.416788</v>
       </c>
       <c r="J46" t="n">
-        <v>183129.140108</v>
+        <v>187058.350885</v>
       </c>
       <c r="K46" t="n">
-        <v>230595.767578</v>
+        <v>235853.717622</v>
       </c>
       <c r="L46" t="n">
-        <v>290242.607398</v>
+        <v>297210.580499</v>
       </c>
       <c r="M46" t="n">
-        <v>355509.177967</v>
+        <v>364473.485634</v>
       </c>
       <c r="N46" t="n">
-        <v>429334.707394</v>
+        <v>440700.922573</v>
       </c>
       <c r="O46" t="n">
-        <v>516057.210398</v>
+        <v>530432.293346</v>
       </c>
       <c r="P46" t="n">
-        <v>617860.5345449999</v>
+        <v>636038.034371</v>
       </c>
       <c r="Q46" t="n">
-        <v>735485.004606</v>
+        <v>758401.6528</v>
       </c>
       <c r="R46" t="n">
-        <v>868533.259238</v>
+        <v>897307.257638</v>
       </c>
       <c r="S46" t="n">
-        <v>1017281.735225</v>
+        <v>1053212.901653</v>
       </c>
       <c r="T46" t="n">
-        <v>1179602.819104</v>
+        <v>1224160.884797</v>
       </c>
       <c r="U46" t="n">
-        <v>1360258.435234</v>
+        <v>1415401.157072</v>
       </c>
       <c r="V46" t="n">
-        <v>1573829.74526</v>
+        <v>1642264.714415</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1611404.720493</v>
+        <v>1617574.414067</v>
       </c>
       <c r="F47" t="n">
-        <v>1677993.110949</v>
+        <v>1689263.075686</v>
       </c>
       <c r="G47" t="n">
-        <v>1669254.854181</v>
+        <v>1686345.946888</v>
       </c>
       <c r="H47" t="n">
-        <v>1677060.891585</v>
+        <v>1700651.833953</v>
       </c>
       <c r="I47" t="n">
-        <v>1781124.399029</v>
+        <v>1812587.58759</v>
       </c>
       <c r="J47" t="n">
-        <v>1970718.178533</v>
+        <v>2011645.996373</v>
       </c>
       <c r="K47" t="n">
-        <v>2255132.293433</v>
+        <v>2307750.334525</v>
       </c>
       <c r="L47" t="n">
-        <v>2641328.786516</v>
+        <v>2708313.158471</v>
       </c>
       <c r="M47" t="n">
-        <v>3058775.446473</v>
+        <v>3141614.093676</v>
       </c>
       <c r="N47" t="n">
-        <v>3462540.040746</v>
+        <v>3564197.126678</v>
       </c>
       <c r="O47" t="n">
-        <v>3886025.298139</v>
+        <v>4011272.478577</v>
       </c>
       <c r="P47" t="n">
-        <v>4353396.024919</v>
+        <v>4507775.269222</v>
       </c>
       <c r="Q47" t="n">
-        <v>4905395.730602</v>
+        <v>5095684.293611</v>
       </c>
       <c r="R47" t="n">
-        <v>5540038.832195</v>
+        <v>5773327.77906</v>
       </c>
       <c r="S47" t="n">
-        <v>6268682.508481</v>
+        <v>6553859.951493</v>
       </c>
       <c r="T47" t="n">
-        <v>7076879.208542</v>
+        <v>7423479.082084</v>
       </c>
       <c r="U47" t="n">
-        <v>8000179.618672</v>
+        <v>8421138.407668</v>
       </c>
       <c r="V47" t="n">
-        <v>9140347.493635001</v>
+        <v>9654640.749639999</v>
       </c>
     </row>
     <row r="48">
@@ -4022,58 +4022,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>95623.132638</v>
+        <v>96115.340111</v>
       </c>
       <c r="F48" t="n">
-        <v>86963.40426</v>
+        <v>87893.70217800001</v>
       </c>
       <c r="G48" t="n">
-        <v>81521.34510999999</v>
+        <v>82892.844084</v>
       </c>
       <c r="H48" t="n">
-        <v>78361.75342399999</v>
+        <v>80180.34976899999</v>
       </c>
       <c r="I48" t="n">
-        <v>79287.28959</v>
+        <v>81624.904478</v>
       </c>
       <c r="J48" t="n">
-        <v>83086.70526800001</v>
+        <v>86033.903893</v>
       </c>
       <c r="K48" t="n">
-        <v>89870.871703</v>
+        <v>93560.95305900001</v>
       </c>
       <c r="L48" t="n">
-        <v>99732.475272</v>
+        <v>104329.499373</v>
       </c>
       <c r="M48" t="n">
-        <v>110686.997527</v>
+        <v>116279.801692</v>
       </c>
       <c r="N48" t="n">
-        <v>123998.958584</v>
+        <v>130750.339721</v>
       </c>
       <c r="O48" t="n">
-        <v>141074.612616</v>
+        <v>149272.000365</v>
       </c>
       <c r="P48" t="n">
-        <v>162235.612425</v>
+        <v>172239.925197</v>
       </c>
       <c r="Q48" t="n">
-        <v>187780.041239</v>
+        <v>200028.621897</v>
       </c>
       <c r="R48" t="n">
-        <v>217867.163569</v>
+        <v>232870.15655</v>
       </c>
       <c r="S48" t="n">
-        <v>253343.092738</v>
+        <v>271714.565575</v>
       </c>
       <c r="T48" t="n">
-        <v>295089.608981</v>
+        <v>317550.298991</v>
       </c>
       <c r="U48" t="n">
-        <v>345947.786996</v>
+        <v>373438.628988</v>
       </c>
       <c r="V48" t="n">
-        <v>412909.605438</v>
+        <v>446834.542183</v>
       </c>
     </row>
     <row r="49">
@@ -4098,58 +4098,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>551086.248109</v>
+        <v>549725.351635</v>
       </c>
       <c r="F49" t="n">
-        <v>512530.517197</v>
+        <v>510329.719311</v>
       </c>
       <c r="G49" t="n">
-        <v>471818.864075</v>
+        <v>469321.614536</v>
       </c>
       <c r="H49" t="n">
-        <v>437383.938675</v>
+        <v>434825.28772</v>
       </c>
       <c r="I49" t="n">
-        <v>423117.252387</v>
+        <v>420446.927747</v>
       </c>
       <c r="J49" t="n">
-        <v>423362.548753</v>
+        <v>420442.22047</v>
       </c>
       <c r="K49" t="n">
-        <v>437016.578936</v>
+        <v>433667.598743</v>
       </c>
       <c r="L49" t="n">
-        <v>461898.047618</v>
+        <v>457917.005027</v>
       </c>
       <c r="M49" t="n">
-        <v>486774.20715</v>
+        <v>482051.16314</v>
       </c>
       <c r="N49" t="n">
-        <v>517025.58866</v>
+        <v>511381.9619</v>
       </c>
       <c r="O49" t="n">
-        <v>555834.521464</v>
+        <v>549015.9154919999</v>
       </c>
       <c r="P49" t="n">
-        <v>601520.913741</v>
+        <v>593236.859858</v>
       </c>
       <c r="Q49" t="n">
-        <v>651206.844449</v>
+        <v>641129.08979</v>
       </c>
       <c r="R49" t="n">
-        <v>701978.609807</v>
+        <v>689740.552231</v>
       </c>
       <c r="S49" t="n">
-        <v>751572.860569</v>
+        <v>736724.8909239999</v>
       </c>
       <c r="T49" t="n">
-        <v>796135.20589</v>
+        <v>778180.7357120001</v>
       </c>
       <c r="U49" t="n">
-        <v>834272.591487</v>
+        <v>812547.559339</v>
       </c>
       <c r="V49" t="n">
-        <v>866607.586519</v>
+        <v>840133.315697</v>
       </c>
     </row>
     <row r="50">
@@ -4174,58 +4174,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14720.299492</v>
+        <v>14685.203413</v>
       </c>
       <c r="F50" t="n">
-        <v>12827.723912</v>
+        <v>12774.927741</v>
       </c>
       <c r="G50" t="n">
-        <v>10841.100257</v>
+        <v>10787.258879</v>
       </c>
       <c r="H50" t="n">
-        <v>9257.087361</v>
+        <v>9207.73265</v>
       </c>
       <c r="I50" t="n">
-        <v>8355.740471999999</v>
+        <v>8309.094595</v>
       </c>
       <c r="J50" t="n">
-        <v>7918.656129</v>
+        <v>7871.402827</v>
       </c>
       <c r="K50" t="n">
-        <v>7816.164224</v>
+        <v>7765.045698</v>
       </c>
       <c r="L50" t="n">
-        <v>7959.495426</v>
+        <v>7901.277992</v>
       </c>
       <c r="M50" t="n">
-        <v>8158.470345</v>
+        <v>8091.14213</v>
       </c>
       <c r="N50" t="n">
-        <v>8467.563735</v>
+        <v>8388.443864999999</v>
       </c>
       <c r="O50" t="n">
-        <v>8933.498</v>
+        <v>8839.165833999999</v>
       </c>
       <c r="P50" t="n">
-        <v>9532.081378999999</v>
+        <v>9418.610608999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>10248.754792</v>
+        <v>10111.138482</v>
       </c>
       <c r="R50" t="n">
-        <v>11039.892683</v>
+        <v>10872.270062</v>
       </c>
       <c r="S50" t="n">
-        <v>11873.561853</v>
+        <v>11668.632305</v>
       </c>
       <c r="T50" t="n">
-        <v>12682.98545</v>
+        <v>12432.656693</v>
       </c>
       <c r="U50" t="n">
-        <v>13444.868953</v>
+        <v>13138.476754</v>
       </c>
       <c r="V50" t="n">
-        <v>14177.031886</v>
+        <v>13798.908294</v>
       </c>
     </row>
     <row r="51">
@@ -4250,58 +4250,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>149292.962598</v>
+        <v>149535.854674</v>
       </c>
       <c r="F51" t="n">
-        <v>127224.044455</v>
+        <v>127771.188645</v>
       </c>
       <c r="G51" t="n">
-        <v>113738.648771</v>
+        <v>114648.154543</v>
       </c>
       <c r="H51" t="n">
-        <v>106353.901255</v>
+        <v>107643.481033</v>
       </c>
       <c r="I51" t="n">
-        <v>106493.547097</v>
+        <v>108210.564183</v>
       </c>
       <c r="J51" t="n">
-        <v>111478.623108</v>
+        <v>113677.647906</v>
       </c>
       <c r="K51" t="n">
-        <v>120536.788635</v>
+        <v>123306.498601</v>
       </c>
       <c r="L51" t="n">
-        <v>132913.779107</v>
+        <v>136361.511758</v>
       </c>
       <c r="M51" t="n">
-        <v>145574.436867</v>
+        <v>149747.874154</v>
       </c>
       <c r="N51" t="n">
-        <v>159972.330114</v>
+        <v>164969.541046</v>
       </c>
       <c r="O51" t="n">
-        <v>177541.763174</v>
+        <v>183535.099723</v>
       </c>
       <c r="P51" t="n">
-        <v>198226.048947</v>
+        <v>205429.389898</v>
       </c>
       <c r="Q51" t="n">
-        <v>221952.514098</v>
+        <v>230620.041494</v>
       </c>
       <c r="R51" t="n">
-        <v>248118.511953</v>
+        <v>258529.316543</v>
       </c>
       <c r="S51" t="n">
-        <v>276915.318335</v>
+        <v>289391.904027</v>
       </c>
       <c r="T51" t="n">
-        <v>308170.519343</v>
+        <v>323070.44192</v>
       </c>
       <c r="U51" t="n">
-        <v>343282.269876</v>
+        <v>361049.393381</v>
       </c>
       <c r="V51" t="n">
-        <v>387317.119667</v>
+        <v>408670.684828</v>
       </c>
     </row>
     <row r="52">
@@ -4326,58 +4326,58 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>152825.837724</v>
+        <v>152666.4775</v>
       </c>
       <c r="F52" t="n">
-        <v>116521.880783</v>
+        <v>116409.504131</v>
       </c>
       <c r="G52" t="n">
-        <v>93873.24334299999</v>
+        <v>93900.511765</v>
       </c>
       <c r="H52" t="n">
-        <v>81278.628203</v>
+        <v>81444.762609</v>
       </c>
       <c r="I52" t="n">
-        <v>76901.297328</v>
+        <v>77189.000611</v>
       </c>
       <c r="J52" t="n">
-        <v>77289.753885</v>
+        <v>77682.536201</v>
       </c>
       <c r="K52" t="n">
-        <v>81430.19087999999</v>
+        <v>81917.977331</v>
       </c>
       <c r="L52" t="n">
-        <v>88424.616532</v>
+        <v>89001.50092799999</v>
       </c>
       <c r="M52" t="n">
-        <v>95816.272384</v>
+        <v>96467.387498</v>
       </c>
       <c r="N52" t="n">
-        <v>104308.623691</v>
+        <v>105026.888432</v>
       </c>
       <c r="O52" t="n">
-        <v>114724.81197</v>
+        <v>115511.553504</v>
       </c>
       <c r="P52" t="n">
-        <v>126945.035676</v>
+        <v>127799.942547</v>
       </c>
       <c r="Q52" t="n">
-        <v>140885.098441</v>
+        <v>141804.417675</v>
       </c>
       <c r="R52" t="n">
-        <v>156151.327285</v>
+        <v>157125.555441</v>
       </c>
       <c r="S52" t="n">
-        <v>172582.276764</v>
+        <v>173592.46283</v>
       </c>
       <c r="T52" t="n">
-        <v>189540.149916</v>
+        <v>190562.414557</v>
       </c>
       <c r="U52" t="n">
-        <v>207215.570903</v>
+        <v>208217.606625</v>
       </c>
       <c r="V52" t="n">
-        <v>226533.833783</v>
+        <v>227468.52605</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>251802.719968</v>
+        <v>251800.293719</v>
       </c>
       <c r="F54" t="n">
-        <v>378690.37292</v>
+        <v>378681.195956</v>
       </c>
       <c r="G54" t="n">
-        <v>515713.506983</v>
+        <v>515688.272267</v>
       </c>
       <c r="H54" t="n">
-        <v>665197.711055</v>
+        <v>665132.109911</v>
       </c>
       <c r="I54" t="n">
-        <v>879608.542773</v>
+        <v>879390.581567</v>
       </c>
       <c r="J54" t="n">
         <v>1926230.404458</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>255108.634632</v>
+        <v>255111.060881</v>
       </c>
       <c r="F55" t="n">
-        <v>356482.915548</v>
+        <v>356492.092513</v>
       </c>
       <c r="G55" t="n">
-        <v>457831.679464</v>
+        <v>457856.91418</v>
       </c>
       <c r="H55" t="n">
-        <v>564419.580339</v>
+        <v>564485.1814830001</v>
       </c>
       <c r="I55" t="n">
-        <v>720563.798525</v>
+        <v>720781.7597319999</v>
       </c>
       <c r="J55" t="n">
         <v>157798.979587</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.843671</v>
+        <v>1.771472</v>
       </c>
       <c r="F58" t="n">
-        <v>5.101265</v>
+        <v>4.901525</v>
       </c>
       <c r="G58" t="n">
-        <v>12.892172</v>
+        <v>12.387492</v>
       </c>
       <c r="H58" t="n">
-        <v>31.260279</v>
+        <v>30.037078</v>
       </c>
       <c r="I58" t="n">
-        <v>95.806944</v>
+        <v>92.06275599999999</v>
       </c>
       <c r="J58" t="n">
         <v>54405.194143</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.364861</v>
+        <v>0.350573</v>
       </c>
       <c r="F59" t="n">
-        <v>1.052943</v>
+        <v>1.011715</v>
       </c>
       <c r="G59" t="n">
-        <v>2.761502</v>
+        <v>2.653399</v>
       </c>
       <c r="H59" t="n">
-        <v>6.755808</v>
+        <v>6.491456</v>
       </c>
       <c r="I59" t="n">
-        <v>20.67267</v>
+        <v>19.864771</v>
       </c>
       <c r="J59" t="n">
         <v>11743.344249</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.899734</v>
+        <v>0.8645</v>
       </c>
       <c r="F60" t="n">
-        <v>1.960774</v>
+        <v>1.884</v>
       </c>
       <c r="G60" t="n">
-        <v>3.899873</v>
+        <v>3.747207</v>
       </c>
       <c r="H60" t="n">
-        <v>7.939388</v>
+        <v>7.628723</v>
       </c>
       <c r="I60" t="n">
-        <v>21.727215</v>
+        <v>20.878104</v>
       </c>
       <c r="J60" t="n">
         <v>11522.624546</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>97213.967424</v>
+        <v>97214.029404</v>
       </c>
       <c r="F61" t="n">
-        <v>106084.480733</v>
+        <v>106084.63922</v>
       </c>
       <c r="G61" t="n">
-        <v>125147.495924</v>
+        <v>125147.794863</v>
       </c>
       <c r="H61" t="n">
-        <v>140427.087241</v>
+        <v>140427.576325</v>
       </c>
       <c r="I61" t="n">
-        <v>160509.482273</v>
+        <v>160510.366777</v>
       </c>
       <c r="J61" t="n">
         <v>180861.430039</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>55485.805884</v>
+        <v>55485.172237</v>
       </c>
       <c r="F62" t="n">
-        <v>64717.975739</v>
+        <v>64716.005383</v>
       </c>
       <c r="G62" t="n">
-        <v>79297.61426</v>
+        <v>79292.54696599999</v>
       </c>
       <c r="H62" t="n">
-        <v>89439.114749</v>
+        <v>89427.281323</v>
       </c>
       <c r="I62" t="n">
-        <v>100509.746798</v>
+        <v>100475.792888</v>
       </c>
       <c r="J62" t="n">
         <v>570149.5349570001</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>34171.850873</v>
+        <v>34171.363113</v>
       </c>
       <c r="F63" t="n">
-        <v>38720.850571</v>
+        <v>38719.427782</v>
       </c>
       <c r="G63" t="n">
-        <v>45803.628627</v>
+        <v>45800.220138</v>
       </c>
       <c r="H63" t="n">
-        <v>51366.685097</v>
+        <v>51358.953623</v>
       </c>
       <c r="I63" t="n">
-        <v>59283.828968</v>
+        <v>59261.30635</v>
       </c>
       <c r="J63" t="n">
         <v>390565.100938</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.16611</v>
+        <v>0.159605</v>
       </c>
       <c r="F64" t="n">
-        <v>0.412373</v>
+        <v>0.396226</v>
       </c>
       <c r="G64" t="n">
-        <v>0.935744</v>
+        <v>0.8991130000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>2.068553</v>
+        <v>1.987611</v>
       </c>
       <c r="I64" t="n">
-        <v>5.910241</v>
+        <v>5.679266</v>
       </c>
       <c r="J64" t="n">
         <v>3193.159658</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>295572.831708</v>
+        <v>295573.501512</v>
       </c>
       <c r="F65" t="n">
-        <v>350019.870427</v>
+        <v>350021.819233</v>
       </c>
       <c r="G65" t="n">
-        <v>455737.118026</v>
+        <v>455741.877065</v>
       </c>
       <c r="H65" t="n">
-        <v>564875.399467</v>
+        <v>564886.3709560001</v>
       </c>
       <c r="I65" t="n">
-        <v>709671.099959</v>
+        <v>709703.023481</v>
       </c>
       <c r="J65" t="n">
         <v>453447.995471</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>104392.592871</v>
+        <v>104392.873437</v>
       </c>
       <c r="F66" t="n">
-        <v>120627.221454</v>
+        <v>120628.022432</v>
       </c>
       <c r="G66" t="n">
-        <v>153392.121436</v>
+        <v>153394.05592</v>
       </c>
       <c r="H66" t="n">
-        <v>185736.919613</v>
+        <v>185741.341576</v>
       </c>
       <c r="I66" t="n">
-        <v>228113.267719</v>
+        <v>228126.059479</v>
       </c>
       <c r="J66" t="n">
         <v>104924.581709</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123860.721207</v>
+        <v>123861.153229</v>
       </c>
       <c r="F67" t="n">
-        <v>146383.962475</v>
+        <v>146385.229318</v>
       </c>
       <c r="G67" t="n">
-        <v>194845.081495</v>
+        <v>194848.323329</v>
       </c>
       <c r="H67" t="n">
-        <v>246619.565082</v>
+        <v>246627.423978</v>
       </c>
       <c r="I67" t="n">
-        <v>314544.721939</v>
+        <v>314568.712375</v>
       </c>
       <c r="J67" t="n">
         <v>53011.848787</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10356.240194</v>
+        <v>10356.148811</v>
       </c>
       <c r="F68" t="n">
-        <v>12442.753675</v>
+        <v>12442.458435</v>
       </c>
       <c r="G68" t="n">
-        <v>17078.540808</v>
+        <v>17077.653247</v>
       </c>
       <c r="H68" t="n">
-        <v>21515.436061</v>
+        <v>21513.028391</v>
       </c>
       <c r="I68" t="n">
-        <v>26305.471003</v>
+        <v>26297.744272</v>
       </c>
       <c r="J68" t="n">
         <v>143149.533637</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.35008</v>
+        <v>0.33637</v>
       </c>
       <c r="F69" t="n">
-        <v>0.959738</v>
+        <v>0.922159</v>
       </c>
       <c r="G69" t="n">
-        <v>2.30163</v>
+        <v>2.21153</v>
       </c>
       <c r="H69" t="n">
-        <v>5.231725</v>
+        <v>5.02701</v>
       </c>
       <c r="I69" t="n">
-        <v>15.159587</v>
+        <v>14.567142</v>
       </c>
       <c r="J69" t="n">
         <v>8370.598039</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78769.857854</v>
+        <v>78770.11665700001</v>
       </c>
       <c r="F70" t="n">
-        <v>87693.037362</v>
+        <v>87693.752077</v>
       </c>
       <c r="G70" t="n">
-        <v>107692.697884</v>
+        <v>107694.382619</v>
       </c>
       <c r="H70" t="n">
-        <v>125127.750615</v>
+        <v>125131.492726</v>
       </c>
       <c r="I70" t="n">
-        <v>147328.202842</v>
+        <v>147338.72569</v>
       </c>
       <c r="J70" t="n">
         <v>33056.637723</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33553.750732</v>
+        <v>33553.629978</v>
       </c>
       <c r="F71" t="n">
-        <v>41040.056563</v>
+        <v>41039.653689</v>
       </c>
       <c r="G71" t="n">
-        <v>50836.739636</v>
+        <v>50835.683618</v>
       </c>
       <c r="H71" t="n">
-        <v>57802.807908</v>
+        <v>57800.314768</v>
       </c>
       <c r="I71" t="n">
-        <v>65988.16177799999</v>
+        <v>65980.85020299999</v>
       </c>
       <c r="J71" t="n">
         <v>179555.063309</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70674.497959</v>
+        <v>70674.59020200001</v>
       </c>
       <c r="F72" t="n">
-        <v>72703.55525200001</v>
+        <v>72703.786863</v>
       </c>
       <c r="G72" t="n">
-        <v>83133.359407</v>
+        <v>83133.831687</v>
       </c>
       <c r="H72" t="n">
-        <v>91410.316653</v>
+        <v>91411.21335400001</v>
       </c>
       <c r="I72" t="n">
-        <v>103657.512513</v>
+        <v>103659.635844</v>
       </c>
       <c r="J72" t="n">
         <v>96445.523724</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>530.105491</v>
+        <v>529.790891</v>
       </c>
       <c r="F73" t="n">
-        <v>462.133243</v>
+        <v>461.492036</v>
       </c>
       <c r="G73" t="n">
-        <v>413.398472</v>
+        <v>412.36288</v>
       </c>
       <c r="H73" t="n">
-        <v>385.310423</v>
+        <v>383.579087</v>
       </c>
       <c r="I73" t="n">
-        <v>448.019478</v>
+        <v>443.801036</v>
       </c>
       <c r="J73" t="n">
         <v>55055.300206</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.136348</v>
+        <v>0.131008</v>
       </c>
       <c r="F74" t="n">
-        <v>0.44716</v>
+        <v>0.429652</v>
       </c>
       <c r="G74" t="n">
-        <v>1.128536</v>
+        <v>1.084358</v>
       </c>
       <c r="H74" t="n">
-        <v>2.538314</v>
+        <v>2.438991</v>
       </c>
       <c r="I74" t="n">
-        <v>7.126475</v>
+        <v>6.847968</v>
       </c>
       <c r="J74" t="n">
         <v>3778.609532</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>12296.617882</v>
+        <v>12296.66457</v>
       </c>
       <c r="F75" t="n">
-        <v>15006.281735</v>
+        <v>15006.385564</v>
       </c>
       <c r="G75" t="n">
-        <v>19143.461814</v>
+        <v>19143.56035</v>
       </c>
       <c r="H75" t="n">
-        <v>24471.967605</v>
+        <v>24471.95782</v>
       </c>
       <c r="I75" t="n">
-        <v>30139.547797</v>
+        <v>30139.104928</v>
       </c>
       <c r="J75" t="n">
         <v>40373.656288</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11145.811073</v>
+        <v>11145.251825</v>
       </c>
       <c r="F76" t="n">
-        <v>14020.510692</v>
+        <v>14018.407542</v>
       </c>
       <c r="G76" t="n">
-        <v>14605.735208</v>
+        <v>14601.128744</v>
       </c>
       <c r="H76" t="n">
-        <v>15873.593368</v>
+        <v>15863.588297</v>
       </c>
       <c r="I76" t="n">
-        <v>18084.987218</v>
+        <v>18057.003727</v>
       </c>
       <c r="J76" t="n">
         <v>201873.127013</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48970.783812</v>
+        <v>48971.13805</v>
       </c>
       <c r="F77" t="n">
-        <v>67861.67959299999</v>
+        <v>67862.81297</v>
       </c>
       <c r="G77" t="n">
-        <v>90877.416744</v>
+        <v>90879.882394</v>
       </c>
       <c r="H77" t="n">
-        <v>112976.044955</v>
+        <v>112981.377517</v>
       </c>
       <c r="I77" t="n">
-        <v>129093.082795</v>
+        <v>129107.364234</v>
       </c>
       <c r="J77" t="n">
         <v>58388.250968</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>36691.473898</v>
+        <v>36690.872083</v>
       </c>
       <c r="F78" t="n">
-        <v>38907.18689</v>
+        <v>38905.361304</v>
       </c>
       <c r="G78" t="n">
-        <v>42122.969673</v>
+        <v>42118.556555</v>
       </c>
       <c r="H78" t="n">
-        <v>48758.528112</v>
+        <v>48747.811936</v>
       </c>
       <c r="I78" t="n">
-        <v>58044.218066</v>
+        <v>58011.85555</v>
       </c>
       <c r="J78" t="n">
         <v>285296.902229</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>41002.633313</v>
+        <v>41002.96852</v>
       </c>
       <c r="F79" t="n">
-        <v>65465.511002</v>
+        <v>65466.790499</v>
       </c>
       <c r="G79" t="n">
-        <v>109167.143154</v>
+        <v>109170.780993</v>
       </c>
       <c r="H79" t="n">
-        <v>171683.515791</v>
+        <v>171693.695647</v>
       </c>
       <c r="I79" t="n">
-        <v>243895.359626</v>
+        <v>243929.078543</v>
       </c>
       <c r="J79" t="n">
         <v>87551.979018</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6827.699625</v>
+        <v>6827.740361</v>
       </c>
       <c r="F80" t="n">
-        <v>7104.627736</v>
+        <v>7104.728048</v>
       </c>
       <c r="G80" t="n">
-        <v>7840.890654</v>
+        <v>7841.072014</v>
       </c>
       <c r="H80" t="n">
-        <v>9501.300576</v>
+        <v>9501.681005</v>
       </c>
       <c r="I80" t="n">
-        <v>11890.313923</v>
+        <v>11891.402348</v>
       </c>
       <c r="J80" t="n">
         <v>7971.127992</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>62593.054711</v>
+        <v>62593.582594</v>
       </c>
       <c r="F81" t="n">
-        <v>103767.733028</v>
+        <v>103769.84558</v>
       </c>
       <c r="G81" t="n">
-        <v>176998.177424</v>
+        <v>177004.436683</v>
       </c>
       <c r="H81" t="n">
-        <v>285559.081017</v>
+        <v>285577.360633</v>
       </c>
       <c r="I81" t="n">
-        <v>418608.566021</v>
+        <v>418671.746025</v>
       </c>
       <c r="J81" t="n">
         <v>114958.725418</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>392.778084</v>
+        <v>392.636313</v>
       </c>
       <c r="F82" t="n">
-        <v>485.664305</v>
+        <v>485.160178</v>
       </c>
       <c r="G82" t="n">
-        <v>609.925541</v>
+        <v>608.5358189999999</v>
       </c>
       <c r="H82" t="n">
-        <v>803.030332</v>
+        <v>799.219994</v>
       </c>
       <c r="I82" t="n">
-        <v>1087.426977</v>
+        <v>1074.910692</v>
       </c>
       <c r="J82" t="n">
         <v>88727.078331</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>25308.080601</v>
+        <v>25308.078685</v>
       </c>
       <c r="F83" t="n">
-        <v>41393.505542</v>
+        <v>41393.208838</v>
       </c>
       <c r="G83" t="n">
-        <v>68157.37328699999</v>
+        <v>68155.139946</v>
       </c>
       <c r="H83" t="n">
-        <v>105145.774144</v>
+        <v>105136.143052</v>
       </c>
       <c r="I83" t="n">
-        <v>146626.200309</v>
+        <v>146587.236684</v>
       </c>
       <c r="J83" t="n">
         <v>483412.146609</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>85655.01111199999</v>
+        <v>85655.97382100001</v>
       </c>
       <c r="F86" t="n">
-        <v>105592.92507</v>
+        <v>105595.995149</v>
       </c>
       <c r="G86" t="n">
-        <v>110079.579298</v>
+        <v>110086.020956</v>
       </c>
       <c r="H86" t="n">
-        <v>119510.338906</v>
+        <v>119524.312492</v>
       </c>
       <c r="I86" t="n">
-        <v>133436.086713</v>
+        <v>133474.482819</v>
       </c>
       <c r="J86" t="n">
         <v>124143.821262</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6617.03662</v>
+        <v>6616.271962</v>
       </c>
       <c r="F87" t="n">
-        <v>9194.174498</v>
+        <v>9191.581991999999</v>
       </c>
       <c r="G87" t="n">
-        <v>11052.373867</v>
+        <v>11046.285417</v>
       </c>
       <c r="H87" t="n">
-        <v>13577.098284</v>
+        <v>13562.498668</v>
       </c>
       <c r="I87" t="n">
-        <v>16964.775998</v>
+        <v>16921.178404</v>
       </c>
       <c r="J87" t="n">
         <v>53122.026396</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>183055.137839</v>
+        <v>183055.266996</v>
       </c>
       <c r="F88" t="n">
-        <v>205663.282656</v>
+        <v>205663.561262</v>
       </c>
       <c r="G88" t="n">
-        <v>202236.530437</v>
+        <v>202236.776513</v>
       </c>
       <c r="H88" t="n">
-        <v>217939.291462</v>
+        <v>217939.611986</v>
       </c>
       <c r="I88" t="n">
-        <v>249713.492556</v>
+        <v>249714.65744</v>
       </c>
       <c r="J88" t="n">
         <v>293153.684692</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>39952.366188</v>
+        <v>39953.867561</v>
       </c>
       <c r="F89" t="n">
-        <v>47627.281157</v>
+        <v>47631.747797</v>
       </c>
       <c r="G89" t="n">
-        <v>50374.528083</v>
+        <v>50383.932555</v>
       </c>
       <c r="H89" t="n">
-        <v>55772.848719</v>
+        <v>55793.556854</v>
       </c>
       <c r="I89" t="n">
-        <v>63419.13205</v>
+        <v>63477.140572</v>
       </c>
       <c r="J89" t="n">
         <v>32202.105115</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>129239.460718</v>
+        <v>129239.542586</v>
       </c>
       <c r="F90" t="n">
-        <v>156001.061268</v>
+        <v>156001.445137</v>
       </c>
       <c r="G90" t="n">
-        <v>168549.703892</v>
+        <v>168550.787253</v>
       </c>
       <c r="H90" t="n">
-        <v>192305.871883</v>
+        <v>192308.908341</v>
       </c>
       <c r="I90" t="n">
-        <v>225161.722427</v>
+        <v>225171.846964</v>
       </c>
       <c r="J90" t="n">
         <v>256199.648813</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60716.871257</v>
+        <v>60718.255706</v>
       </c>
       <c r="F91" t="n">
-        <v>74903.76199</v>
+        <v>74908.07348200001</v>
       </c>
       <c r="G91" t="n">
-        <v>79008.76525500001</v>
+        <v>79017.858313</v>
       </c>
       <c r="H91" t="n">
-        <v>85357.17251600001</v>
+        <v>85376.718957</v>
       </c>
       <c r="I91" t="n">
-        <v>93358.038522</v>
+        <v>93410.52996699999</v>
       </c>
       <c r="J91" t="n">
         <v>67367.729985</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65760.00997699999</v>
+        <v>65762.804604</v>
       </c>
       <c r="F92" t="n">
-        <v>81795.993219</v>
+        <v>81804.685254</v>
       </c>
       <c r="G92" t="n">
-        <v>89028.48645</v>
+        <v>89047.346272</v>
       </c>
       <c r="H92" t="n">
-        <v>98777.71221500001</v>
+        <v>98819.34770899999</v>
       </c>
       <c r="I92" t="n">
-        <v>110294.258117</v>
+        <v>110408.818683</v>
       </c>
       <c r="J92" t="n">
         <v>45089.589277</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>907.916497</v>
+        <v>907.499386</v>
       </c>
       <c r="F93" t="n">
-        <v>1196.444299</v>
+        <v>1195.101907</v>
       </c>
       <c r="G93" t="n">
-        <v>1404.667077</v>
+        <v>1401.605839</v>
       </c>
       <c r="H93" t="n">
-        <v>1748.601532</v>
+        <v>1741.290195</v>
       </c>
       <c r="I93" t="n">
-        <v>2302.077481</v>
+        <v>2280.176826</v>
       </c>
       <c r="J93" t="n">
         <v>19059.467317</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>384050.831187</v>
+        <v>384039.912255</v>
       </c>
       <c r="F94" t="n">
-        <v>509106.742343</v>
+        <v>509072.152217</v>
       </c>
       <c r="G94" t="n">
-        <v>562665.492961</v>
+        <v>562591.2090349999</v>
       </c>
       <c r="H94" t="n">
-        <v>637421.812409</v>
+        <v>637257.5458580001</v>
       </c>
       <c r="I94" t="n">
-        <v>734500.913492</v>
+        <v>734044.064043</v>
       </c>
       <c r="J94" t="n">
         <v>1164881.827677</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>255613.336933</v>
+        <v>255617.572739</v>
       </c>
       <c r="F95" t="n">
-        <v>339228.4641</v>
+        <v>339242.990425</v>
       </c>
       <c r="G95" t="n">
-        <v>380481.353475</v>
+        <v>380514.456863</v>
       </c>
       <c r="H95" t="n">
-        <v>434555.188624</v>
+        <v>434631.32503</v>
       </c>
       <c r="I95" t="n">
-        <v>500942.586673</v>
+        <v>501160.036243</v>
       </c>
       <c r="J95" t="n">
         <v>420983.30807</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92850.73482</v>
+        <v>92851.050932</v>
       </c>
       <c r="F96" t="n">
-        <v>109036.502752</v>
+        <v>109037.451173</v>
       </c>
       <c r="G96" t="n">
-        <v>107950.542233</v>
+        <v>107952.290666</v>
       </c>
       <c r="H96" t="n">
-        <v>115354.648277</v>
+        <v>115358.248268</v>
       </c>
       <c r="I96" t="n">
-        <v>130157.871946</v>
+        <v>130167.876858</v>
       </c>
       <c r="J96" t="n">
         <v>143580.76317</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>46707.756851</v>
+        <v>46708.451454</v>
       </c>
       <c r="F97" t="n">
-        <v>50763.756624</v>
+        <v>50765.604182</v>
       </c>
       <c r="G97" t="n">
-        <v>48814.580975</v>
+        <v>48818.03432</v>
       </c>
       <c r="H97" t="n">
-        <v>51895.968504</v>
+        <v>51903.188973</v>
       </c>
       <c r="I97" t="n">
-        <v>59018.87664</v>
+        <v>59039.023796</v>
       </c>
       <c r="J97" t="n">
         <v>54791.779925</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>426903.572328</v>
+        <v>426912.577529</v>
       </c>
       <c r="F98" t="n">
-        <v>432480.72081</v>
+        <v>432504.127323</v>
       </c>
       <c r="G98" t="n">
-        <v>472489.481917</v>
+        <v>472542.026896</v>
       </c>
       <c r="H98" t="n">
-        <v>493436.059538</v>
+        <v>493548.222632</v>
       </c>
       <c r="I98" t="n">
-        <v>533036.568041</v>
+        <v>533343.902522</v>
       </c>
       <c r="J98" t="n">
         <v>259534.80329</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>160750.138396</v>
+        <v>160746.84713</v>
       </c>
       <c r="F99" t="n">
-        <v>188537.502488</v>
+        <v>188527.819995</v>
       </c>
       <c r="G99" t="n">
-        <v>241351.382256</v>
+        <v>241326.509376</v>
       </c>
       <c r="H99" t="n">
-        <v>284595.650158</v>
+        <v>284536.987775</v>
       </c>
       <c r="I99" t="n">
-        <v>335127.111101</v>
+        <v>334955.632514</v>
       </c>
       <c r="J99" t="n">
         <v>608150.513193</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>207470.501559</v>
+        <v>207474.194484</v>
       </c>
       <c r="F100" t="n">
-        <v>208655.801133</v>
+        <v>208665.381148</v>
       </c>
       <c r="G100" t="n">
-        <v>230866.038789</v>
+        <v>230887.905943</v>
       </c>
       <c r="H100" t="n">
-        <v>244379.939326</v>
+        <v>244427.391254</v>
       </c>
       <c r="I100" t="n">
-        <v>266977.280943</v>
+        <v>267109.044509</v>
       </c>
       <c r="J100" t="n">
         <v>156190.645053</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>457353.588857</v>
+        <v>457366.913172</v>
       </c>
       <c r="F101" t="n">
-        <v>492953.586988</v>
+        <v>492990.146874</v>
       </c>
       <c r="G101" t="n">
-        <v>579849.981694</v>
+        <v>579937.6184790001</v>
       </c>
       <c r="H101" t="n">
-        <v>640063.266955</v>
+        <v>640259.744588</v>
       </c>
       <c r="I101" t="n">
-        <v>715759.94586</v>
+        <v>716314.939524</v>
       </c>
       <c r="J101" t="n">
         <v>191542.519577</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>999169.181066</v>
+        <v>999159.831085</v>
       </c>
       <c r="F102" t="n">
-        <v>1139293.392843</v>
+        <v>1139267.20804</v>
       </c>
       <c r="G102" t="n">
-        <v>1433143.146861</v>
+        <v>1433078.234621</v>
       </c>
       <c r="H102" t="n">
-        <v>1683640.595803</v>
+        <v>1683490.049098</v>
       </c>
       <c r="I102" t="n">
-        <v>1992001.298656</v>
+        <v>1991563.151881</v>
       </c>
       <c r="J102" t="n">
         <v>2949243.966575</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1701869.934673</v>
+        <v>1701876.062878</v>
       </c>
       <c r="F103" t="n">
-        <v>1661806.727475</v>
+        <v>1661824.061359</v>
       </c>
       <c r="G103" t="n">
-        <v>1765903.615379</v>
+        <v>1765945.710072</v>
       </c>
       <c r="H103" t="n">
-        <v>1806535.130327</v>
+        <v>1806629.92597</v>
       </c>
       <c r="I103" t="n">
-        <v>1925033.072442</v>
+        <v>1925302.251338</v>
       </c>
       <c r="J103" t="n">
         <v>1865231.591021</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>123655.666778</v>
+        <v>123652.820697</v>
       </c>
       <c r="F104" t="n">
-        <v>135527.291662</v>
+        <v>135519.525187</v>
       </c>
       <c r="G104" t="n">
-        <v>162636.023355</v>
+        <v>162617.453926</v>
       </c>
       <c r="H104" t="n">
-        <v>185481.742055</v>
+        <v>185439.464269</v>
       </c>
       <c r="I104" t="n">
-        <v>215582.885682</v>
+        <v>215460.749224</v>
       </c>
       <c r="J104" t="n">
         <v>404174.346883</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48835.459948</v>
+        <v>48833.57776</v>
       </c>
       <c r="F105" t="n">
-        <v>54401.308183</v>
+        <v>54396.0907</v>
       </c>
       <c r="G105" t="n">
-        <v>67141.64765300001</v>
+        <v>67128.793221</v>
       </c>
       <c r="H105" t="n">
-        <v>77391.83582599999</v>
+        <v>77362.29634099999</v>
       </c>
       <c r="I105" t="n">
-        <v>90155.717563</v>
+        <v>90070.51514</v>
       </c>
       <c r="J105" t="n">
         <v>208694.770851</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1145560.716425</v>
+        <v>1145564.205524</v>
       </c>
       <c r="F106" t="n">
-        <v>1316452.284957</v>
+        <v>1316462.946072</v>
       </c>
       <c r="G106" t="n">
-        <v>1683287.344271</v>
+        <v>1683315.921306</v>
       </c>
       <c r="H106" t="n">
-        <v>1991809.475223</v>
+        <v>1991879.80268</v>
       </c>
       <c r="I106" t="n">
-        <v>2353032.863941</v>
+        <v>2353247.144704</v>
       </c>
       <c r="J106" t="n">
         <v>2586180.113376</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>9021.973555</v>
+        <v>9021.015718000001</v>
       </c>
       <c r="F107" t="n">
-        <v>10930.914523</v>
+        <v>10927.992463</v>
       </c>
       <c r="G107" t="n">
-        <v>13705.230628</v>
+        <v>13697.888279</v>
       </c>
       <c r="H107" t="n">
-        <v>15949.342271</v>
+        <v>15932.282248</v>
       </c>
       <c r="I107" t="n">
-        <v>18953.024304</v>
+        <v>18902.927942</v>
       </c>
       <c r="J107" t="n">
         <v>83997.152707</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>156732.074756</v>
+        <v>156721.284143</v>
       </c>
       <c r="F108" t="n">
-        <v>171403.10326</v>
+        <v>171373.571069</v>
       </c>
       <c r="G108" t="n">
-        <v>201678.044555</v>
+        <v>201608.595609</v>
       </c>
       <c r="H108" t="n">
-        <v>222889.800954</v>
+        <v>222736.705099</v>
       </c>
       <c r="I108" t="n">
-        <v>251320.899437</v>
+        <v>250893.748778</v>
       </c>
       <c r="J108" t="n">
         <v>785883.660113</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>216531.262359</v>
+        <v>216534.620529</v>
       </c>
       <c r="F109" t="n">
-        <v>237347.870332</v>
+        <v>237357.317912</v>
       </c>
       <c r="G109" t="n">
-        <v>298027.692656</v>
+        <v>298051.948919</v>
       </c>
       <c r="H109" t="n">
-        <v>360078.737686</v>
+        <v>360138.220882</v>
       </c>
       <c r="I109" t="n">
-        <v>444013.3003</v>
+        <v>444197.963539</v>
       </c>
       <c r="J109" t="n">
         <v>330461.450711</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>830316.18441</v>
+        <v>830339.497906</v>
       </c>
       <c r="F110" t="n">
-        <v>966639.4179689999</v>
+        <v>966708.443451</v>
       </c>
       <c r="G110" t="n">
-        <v>1237337.620194</v>
+        <v>1237517.471469</v>
       </c>
       <c r="H110" t="n">
-        <v>1459479.822191</v>
+        <v>1459910.344672</v>
       </c>
       <c r="I110" t="n">
-        <v>1711977.198037</v>
+        <v>1713252.218557</v>
       </c>
       <c r="J110" t="n">
         <v>537934.999414</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>724005.888948</v>
+        <v>724001.607552</v>
       </c>
       <c r="F111" t="n">
-        <v>816619.3039910001</v>
+        <v>816607.6461210001</v>
       </c>
       <c r="G111" t="n">
-        <v>998962.998247</v>
+        <v>998935.592799</v>
       </c>
       <c r="H111" t="n">
-        <v>1140252.744149</v>
+        <v>1140192.499615</v>
       </c>
       <c r="I111" t="n">
-        <v>1321192.129171</v>
+        <v>1321023.875362</v>
       </c>
       <c r="J111" t="n">
         <v>1783180.604785</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>597104.3559420001</v>
+        <v>597075.443892</v>
       </c>
       <c r="F112" t="n">
-        <v>683694.383673</v>
+        <v>683611.332572</v>
       </c>
       <c r="G112" t="n">
-        <v>865728.1697889999</v>
+        <v>865516.74733</v>
       </c>
       <c r="H112" t="n">
-        <v>1020351.739134</v>
+        <v>1019851.944473</v>
       </c>
       <c r="I112" t="n">
-        <v>1210347.763806</v>
+        <v>1208872.99375</v>
       </c>
       <c r="J112" t="n">
         <v>3244095.730515</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>57867.447814</v>
+        <v>57867.423187</v>
       </c>
       <c r="F113" t="n">
-        <v>51554.50673</v>
+        <v>51554.443344</v>
       </c>
       <c r="G113" t="n">
-        <v>53648.378023</v>
+        <v>53648.241423</v>
       </c>
       <c r="H113" t="n">
-        <v>64793.287773</v>
+        <v>64792.964436</v>
       </c>
       <c r="I113" t="n">
-        <v>75365.574934</v>
+        <v>75364.696161</v>
       </c>
       <c r="J113" t="n">
         <v>98541.180308</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28456.411849</v>
+        <v>28456.513683</v>
       </c>
       <c r="F114" t="n">
-        <v>35796.946704</v>
+        <v>35797.269695</v>
       </c>
       <c r="G114" t="n">
-        <v>55529.261789</v>
+        <v>55530.259867</v>
       </c>
       <c r="H114" t="n">
-        <v>87558.02761400001</v>
+        <v>87561.161378</v>
       </c>
       <c r="I114" t="n">
-        <v>116191.426081</v>
+        <v>116201.796182</v>
       </c>
       <c r="J114" t="n">
         <v>26818.241805</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>114013.306337</v>
+        <v>114013.22913</v>
       </c>
       <c r="F115" t="n">
-        <v>116778.574316</v>
+        <v>116778.31471</v>
       </c>
       <c r="G115" t="n">
-        <v>152098.759824</v>
+        <v>152097.898346</v>
       </c>
       <c r="H115" t="n">
-        <v>217395.579858</v>
+        <v>217392.769431</v>
       </c>
       <c r="I115" t="n">
-        <v>280511.370778</v>
+        <v>280501.87945</v>
       </c>
       <c r="J115" t="n">
         <v>460654.534724</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25216.489193</v>
+        <v>25216.445436</v>
       </c>
       <c r="F116" t="n">
-        <v>25463.482162</v>
+        <v>25463.368969</v>
       </c>
       <c r="G116" t="n">
-        <v>29444.637933</v>
+        <v>29444.36951</v>
       </c>
       <c r="H116" t="n">
-        <v>34829.136882</v>
+        <v>34828.488809</v>
       </c>
       <c r="I116" t="n">
-        <v>41495.846906</v>
+        <v>41493.885623</v>
       </c>
       <c r="J116" t="n">
         <v>13382.864881</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>34799.907018</v>
+        <v>34799.883986</v>
       </c>
       <c r="F117" t="n">
-        <v>43402.147104</v>
+        <v>43402.08405</v>
       </c>
       <c r="G117" t="n">
-        <v>55345.434685</v>
+        <v>55345.282924</v>
       </c>
       <c r="H117" t="n">
-        <v>68823.551909</v>
+        <v>68823.18407</v>
       </c>
       <c r="I117" t="n">
-        <v>83883.564044</v>
+        <v>83882.453081</v>
       </c>
       <c r="J117" t="n">
         <v>80719.951514</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>65563.630427</v>
+        <v>65563.615164</v>
       </c>
       <c r="F118" t="n">
-        <v>64673.737951</v>
+        <v>64673.698949</v>
       </c>
       <c r="G118" t="n">
-        <v>72613.109643</v>
+        <v>72613.015205</v>
       </c>
       <c r="H118" t="n">
-        <v>83832.47326499999</v>
+        <v>83832.239573</v>
       </c>
       <c r="I118" t="n">
-        <v>98154.251128</v>
+        <v>98153.529777</v>
       </c>
       <c r="J118" t="n">
         <v>102496.145627</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>13864.270197</v>
+        <v>13864.26848</v>
       </c>
       <c r="F119" t="n">
-        <v>16510.15732</v>
+        <v>16510.155735</v>
       </c>
       <c r="G119" t="n">
-        <v>22040.417887</v>
+        <v>22040.421556</v>
       </c>
       <c r="H119" t="n">
-        <v>29096.111088</v>
+        <v>29096.13586</v>
       </c>
       <c r="I119" t="n">
-        <v>37488.533946</v>
+        <v>37488.64437</v>
       </c>
       <c r="J119" t="n">
         <v>49958.468351</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9960.07308</v>
+        <v>9960.060742</v>
       </c>
       <c r="F120" t="n">
-        <v>10124.257234</v>
+        <v>10124.225113</v>
       </c>
       <c r="G120" t="n">
-        <v>11810.050808</v>
+        <v>11809.973874</v>
       </c>
       <c r="H120" t="n">
-        <v>14126.232475</v>
+        <v>14126.044373</v>
       </c>
       <c r="I120" t="n">
-        <v>17052.163483</v>
+        <v>17051.586024</v>
       </c>
       <c r="J120" t="n">
         <v>9867.900669000001</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>64609.551242</v>
+        <v>64609.563551</v>
       </c>
       <c r="F121" t="n">
-        <v>75852.604479</v>
+        <v>75852.661311</v>
       </c>
       <c r="G121" t="n">
-        <v>99598.876991</v>
+        <v>99599.07120400001</v>
       </c>
       <c r="H121" t="n">
-        <v>128130.044664</v>
+        <v>128130.618817</v>
       </c>
       <c r="I121" t="n">
-        <v>160009.438663</v>
+        <v>160011.352208</v>
       </c>
       <c r="J121" t="n">
         <v>233019.915051</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>523760.368844</v>
+        <v>523760.452641</v>
       </c>
       <c r="F122" t="n">
-        <v>534380.650009</v>
+        <v>534380.842133</v>
       </c>
       <c r="G122" t="n">
-        <v>627493.8041909999</v>
+        <v>627494.197864</v>
       </c>
       <c r="H122" t="n">
-        <v>758746.4812790001</v>
+        <v>758747.3200609999</v>
       </c>
       <c r="I122" t="n">
-        <v>930016.648187</v>
+        <v>930018.995272</v>
       </c>
       <c r="J122" t="n">
         <v>1192251.289955</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185807.32721</v>
+        <v>185842.860435</v>
       </c>
       <c r="F123" t="n">
-        <v>202441.855946</v>
+        <v>202533.46524</v>
       </c>
       <c r="G123" t="n">
-        <v>233094.067531</v>
+        <v>233291.911144</v>
       </c>
       <c r="H123" t="n">
-        <v>259433.875229</v>
+        <v>259849.868403</v>
       </c>
       <c r="I123" t="n">
-        <v>287602.894152</v>
+        <v>288686.999975</v>
       </c>
       <c r="J123" t="n">
         <v>40167.401294</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500068.401041</v>
+        <v>500095.152009</v>
       </c>
       <c r="F124" t="n">
-        <v>547724.034646</v>
+        <v>547790.343966</v>
       </c>
       <c r="G124" t="n">
-        <v>625321.75887</v>
+        <v>625454.896882</v>
       </c>
       <c r="H124" t="n">
-        <v>694875.935846</v>
+        <v>695140.0190570001</v>
       </c>
       <c r="I124" t="n">
-        <v>774980.029604</v>
+        <v>775633.3306709999</v>
       </c>
       <c r="J124" t="n">
         <v>711444.644208</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>197387.577749</v>
+        <v>197325.293556</v>
       </c>
       <c r="F125" t="n">
-        <v>200999.859131</v>
+        <v>200841.940516</v>
       </c>
       <c r="G125" t="n">
-        <v>211626.572987</v>
+        <v>211295.591362</v>
       </c>
       <c r="H125" t="n">
-        <v>223496.769488</v>
+        <v>222816.693102</v>
       </c>
       <c r="I125" t="n">
-        <v>249463.53001</v>
+        <v>247726.123119</v>
       </c>
       <c r="J125" t="n">
         <v>731876.548246</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4885.173357</v>
+        <v>4885.163111</v>
       </c>
       <c r="F130" t="n">
-        <v>28539.58247</v>
+        <v>28539.396606</v>
       </c>
       <c r="G130" t="n">
-        <v>54745.682085</v>
+        <v>54744.774624</v>
       </c>
       <c r="H130" t="n">
-        <v>90468.615093</v>
+        <v>90464.4795</v>
       </c>
       <c r="I130" t="n">
-        <v>141627.841972</v>
+        <v>141600.764448</v>
       </c>
       <c r="J130" t="n">
         <v>4312459.224822</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.000425</v>
+        <v>0.000107</v>
       </c>
       <c r="F131" t="n">
-        <v>0.010561</v>
+        <v>0.002647</v>
       </c>
       <c r="G131" t="n">
-        <v>0.054113</v>
+        <v>0.013562</v>
       </c>
       <c r="H131" t="n">
-        <v>0.24154</v>
+        <v>0.060537</v>
       </c>
       <c r="I131" t="n">
-        <v>1.525828</v>
+        <v>0.382422</v>
       </c>
       <c r="J131" t="n">
         <v>169075.817842</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>80794.599437</v>
+        <v>80794.608611</v>
       </c>
       <c r="F132" t="n">
-        <v>433634.102264</v>
+        <v>433634.241364</v>
       </c>
       <c r="G132" t="n">
-        <v>744816.776048</v>
+        <v>744817.337316</v>
       </c>
       <c r="H132" t="n">
-        <v>1100130.58167</v>
+        <v>1100132.788311</v>
       </c>
       <c r="I132" t="n">
-        <v>1560864.156745</v>
+        <v>1560877.20543</v>
       </c>
       <c r="J132" t="n">
         <v>271900.280492</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>12208.884236</v>
+        <v>12208.885735</v>
       </c>
       <c r="F133" t="n">
-        <v>93368.34964299999</v>
+        <v>93368.38069200001</v>
       </c>
       <c r="G133" t="n">
-        <v>222946.324362</v>
+        <v>222946.487112</v>
       </c>
       <c r="H133" t="n">
-        <v>420972.220329</v>
+        <v>420972.994834</v>
       </c>
       <c r="I133" t="n">
-        <v>708791.0237359999</v>
+        <v>708796.322985</v>
       </c>
       <c r="J133" t="n">
         <v>240407.454018</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>23317.156439</v>
+        <v>23317.158345</v>
       </c>
       <c r="F134" t="n">
-        <v>118392.394515</v>
+        <v>118392.424133</v>
       </c>
       <c r="G134" t="n">
-        <v>201222.656283</v>
+        <v>201222.780797</v>
       </c>
       <c r="H134" t="n">
-        <v>304720.631771</v>
+        <v>304721.148941</v>
       </c>
       <c r="I134" t="n">
-        <v>451581.879312</v>
+        <v>451585.128652</v>
       </c>
       <c r="J134" t="n">
         <v>156051.046795</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8072.127149</v>
+        <v>8072.128199</v>
       </c>
       <c r="F135" t="n">
-        <v>55627.806239</v>
+        <v>55627.826764</v>
       </c>
       <c r="G135" t="n">
-        <v>123672.06626</v>
+        <v>123672.172589</v>
       </c>
       <c r="H135" t="n">
-        <v>224845.890966</v>
+        <v>224846.398502</v>
       </c>
       <c r="I135" t="n">
-        <v>375236.866215</v>
+        <v>375240.350949</v>
       </c>
       <c r="J135" t="n">
         <v>23286.673588</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1325.397967</v>
+        <v>1325.395913</v>
       </c>
       <c r="F136" t="n">
-        <v>6738.470997</v>
+        <v>6738.445717</v>
       </c>
       <c r="G136" t="n">
-        <v>10672.97862</v>
+        <v>10672.908263</v>
       </c>
       <c r="H136" t="n">
-        <v>14605.096318</v>
+        <v>14604.916615</v>
       </c>
       <c r="I136" t="n">
-        <v>19862.764488</v>
+        <v>19862.019659</v>
       </c>
       <c r="J136" t="n">
         <v>121177.930933</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10012.483696</v>
+        <v>10012.484845</v>
       </c>
       <c r="F137" t="n">
-        <v>55749.94092</v>
+        <v>55749.958723</v>
       </c>
       <c r="G137" t="n">
-        <v>95578.39071599999</v>
+        <v>95578.46225300001</v>
       </c>
       <c r="H137" t="n">
-        <v>140290.551113</v>
+        <v>140290.830734</v>
       </c>
       <c r="I137" t="n">
-        <v>200561.990619</v>
+        <v>200563.650546</v>
       </c>
       <c r="J137" t="n">
         <v>39391.506233</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>116.758167</v>
+        <v>116.757867</v>
       </c>
       <c r="F138" t="n">
-        <v>631.982585</v>
+        <v>631.977806</v>
       </c>
       <c r="G138" t="n">
-        <v>1092.088803</v>
+        <v>1092.070478</v>
       </c>
       <c r="H138" t="n">
-        <v>1601.638801</v>
+        <v>1601.576621</v>
       </c>
       <c r="I138" t="n">
-        <v>2230.421261</v>
+        <v>2230.118319</v>
       </c>
       <c r="J138" t="n">
         <v>38810.465569</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>373.763592</v>
+        <v>373.763601</v>
       </c>
       <c r="F139" t="n">
-        <v>2138.074208</v>
+        <v>2138.074304</v>
       </c>
       <c r="G139" t="n">
-        <v>4051.325704</v>
+        <v>4051.325882</v>
       </c>
       <c r="H139" t="n">
-        <v>6649.619474</v>
+        <v>6649.619615</v>
       </c>
       <c r="I139" t="n">
-        <v>10363.484036</v>
+        <v>10363.483604</v>
       </c>
       <c r="J139" t="n">
         <v>15171.473587</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>518.807852</v>
+        <v>518.804999</v>
       </c>
       <c r="F140" t="n">
-        <v>2707.592143</v>
+        <v>2707.554587</v>
       </c>
       <c r="G140" t="n">
-        <v>4754.894987</v>
+        <v>4754.755947</v>
       </c>
       <c r="H140" t="n">
-        <v>7515.18527</v>
+        <v>7514.65042</v>
       </c>
       <c r="I140" t="n">
-        <v>11747.613806</v>
+        <v>11744.291548</v>
       </c>
       <c r="J140" t="n">
         <v>541457.941429</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1965.078102</v>
+        <v>1965.078332</v>
       </c>
       <c r="F141" t="n">
-        <v>11534.093928</v>
+        <v>11534.097724</v>
       </c>
       <c r="G141" t="n">
-        <v>22242.226335</v>
+        <v>22242.243288</v>
       </c>
       <c r="H141" t="n">
-        <v>36796.171811</v>
+        <v>36796.245475</v>
       </c>
       <c r="I141" t="n">
-        <v>57723.788175</v>
+        <v>57724.264835</v>
       </c>
       <c r="J141" t="n">
         <v>12288.869794</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5828.240781</v>
+        <v>5828.241535</v>
       </c>
       <c r="F142" t="n">
-        <v>54042.881078</v>
+        <v>54042.900484</v>
       </c>
       <c r="G142" t="n">
-        <v>168166.858734</v>
+        <v>168166.990938</v>
       </c>
       <c r="H142" t="n">
-        <v>388984.681527</v>
+        <v>388985.415578</v>
       </c>
       <c r="I142" t="n">
-        <v>747220.13956</v>
+        <v>747225.512357</v>
       </c>
       <c r="J142" t="n">
         <v>349881.025702</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7288.526214</v>
+        <v>7288.582244</v>
       </c>
       <c r="F146" t="n">
-        <v>7358.855691</v>
+        <v>7359.005062</v>
       </c>
       <c r="G146" t="n">
-        <v>7550.295017</v>
+        <v>7550.617332</v>
       </c>
       <c r="H146" t="n">
-        <v>8449.206942999999</v>
+        <v>8449.949887999999</v>
       </c>
       <c r="I146" t="n">
-        <v>10071.59743</v>
+        <v>10073.83664</v>
       </c>
       <c r="J146" t="n">
         <v>4578.692236</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3036.911996</v>
+        <v>3036.857803</v>
       </c>
       <c r="F147" t="n">
-        <v>3548.466832</v>
+        <v>3548.303451</v>
       </c>
       <c r="G147" t="n">
-        <v>4114.158257</v>
+        <v>4113.772706</v>
       </c>
       <c r="H147" t="n">
-        <v>4873.564813</v>
+        <v>4872.643095</v>
       </c>
       <c r="I147" t="n">
-        <v>5901.342055</v>
+        <v>5898.541032</v>
       </c>
       <c r="J147" t="n">
         <v>16560.548895</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>303583.888734</v>
+        <v>303583.886896</v>
       </c>
       <c r="F148" t="n">
-        <v>366411.417849</v>
+        <v>366411.431858</v>
       </c>
       <c r="G148" t="n">
-        <v>451272.962836</v>
+        <v>451273.026072</v>
       </c>
       <c r="H148" t="n">
-        <v>562794.431214</v>
+        <v>562794.609987</v>
       </c>
       <c r="I148" t="n">
-        <v>700350.205616</v>
+        <v>700350.767429</v>
       </c>
       <c r="J148" t="n">
         <v>848333.140773</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48897.919167</v>
+        <v>48895.163489</v>
       </c>
       <c r="F149" t="n">
-        <v>58203.465585</v>
+        <v>58195.343173</v>
       </c>
       <c r="G149" t="n">
-        <v>70782.632211</v>
+        <v>70762.69585800001</v>
       </c>
       <c r="H149" t="n">
-        <v>87436.752399</v>
+        <v>87387.26543699999</v>
       </c>
       <c r="I149" t="n">
-        <v>109878.395712</v>
+        <v>109726.397602</v>
       </c>
       <c r="J149" t="n">
         <v>232279.674995</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>395421.741439</v>
+        <v>395425.774504</v>
       </c>
       <c r="F150" t="n">
-        <v>464217.062509</v>
+        <v>464229.368015</v>
       </c>
       <c r="G150" t="n">
-        <v>551222.079469</v>
+        <v>551249.307731</v>
       </c>
       <c r="H150" t="n">
-        <v>638885.693259</v>
+        <v>638939.026271</v>
       </c>
       <c r="I150" t="n">
-        <v>738059.872643</v>
+        <v>738179.517676</v>
       </c>
       <c r="J150" t="n">
         <v>809895.332421</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>68761.348304</v>
+        <v>68751.150958</v>
       </c>
       <c r="F151" t="n">
-        <v>84198.452406</v>
+        <v>84167.975691</v>
       </c>
       <c r="G151" t="n">
-        <v>104621.905155</v>
+        <v>104547.503537</v>
       </c>
       <c r="H151" t="n">
-        <v>127043.115977</v>
+        <v>126865.733661</v>
       </c>
       <c r="I151" t="n">
-        <v>152844.034435</v>
+        <v>152334.262983</v>
       </c>
       <c r="J151" t="n">
         <v>468036.919734</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>232455.78371</v>
+        <v>232436.932026</v>
       </c>
       <c r="F152" t="n">
-        <v>297909.378507</v>
+        <v>297852.043879</v>
       </c>
       <c r="G152" t="n">
-        <v>362871.374</v>
+        <v>362734.009635</v>
       </c>
       <c r="H152" t="n">
-        <v>420299.030869</v>
+        <v>419981.314502</v>
       </c>
       <c r="I152" t="n">
-        <v>477239.310494</v>
+        <v>476353.423026</v>
       </c>
       <c r="J152" t="n">
         <v>1027747.281498</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>294387.680505</v>
+        <v>294410.580775</v>
       </c>
       <c r="F153" t="n">
-        <v>351786.369739</v>
+        <v>351854.365186</v>
       </c>
       <c r="G153" t="n">
-        <v>440219.629751</v>
+        <v>440386.715293</v>
       </c>
       <c r="H153" t="n">
-        <v>554175.49528</v>
+        <v>554584.022736</v>
       </c>
       <c r="I153" t="n">
-        <v>689429.034594</v>
+        <v>690643.389774</v>
       </c>
       <c r="J153" t="n">
         <v>153144.849394</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>119944.282874</v>
+        <v>119949.154248</v>
       </c>
       <c r="F154" t="n">
-        <v>150845.700606</v>
+        <v>150861.333409</v>
       </c>
       <c r="G154" t="n">
-        <v>183279.399548</v>
+        <v>183316.788081</v>
       </c>
       <c r="H154" t="n">
-        <v>211806.303128</v>
+        <v>211889.028304</v>
       </c>
       <c r="I154" t="n">
-        <v>235652.192045</v>
+        <v>235865.848862</v>
       </c>
       <c r="J154" t="n">
         <v>153880.420963</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>190458.295244</v>
+        <v>190420.691119</v>
       </c>
       <c r="F155" t="n">
-        <v>194179.860067</v>
+        <v>194089.493097</v>
       </c>
       <c r="G155" t="n">
-        <v>231345.504008</v>
+        <v>231147.637385</v>
       </c>
       <c r="H155" t="n">
-        <v>281202.579132</v>
+        <v>280771.428582</v>
       </c>
       <c r="I155" t="n">
-        <v>330520.732969</v>
+        <v>329417.771625</v>
       </c>
       <c r="J155" t="n">
         <v>261727.687822</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>372862.938131</v>
+        <v>373025.407302</v>
       </c>
       <c r="F156" t="n">
-        <v>355430.753697</v>
+        <v>355811.320189</v>
       </c>
       <c r="G156" t="n">
-        <v>390692.691527</v>
+        <v>391530.169002</v>
       </c>
       <c r="H156" t="n">
-        <v>432931.026747</v>
+        <v>434787.105469</v>
       </c>
       <c r="I156" t="n">
-        <v>470036.565072</v>
+        <v>474885.594577</v>
       </c>
       <c r="J156" t="n">
         <v>1118489.576598</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4198.213108</v>
+        <v>4201.152104</v>
       </c>
       <c r="F157" t="n">
-        <v>5050.624854</v>
+        <v>5058.684828</v>
       </c>
       <c r="G157" t="n">
-        <v>6774.752091</v>
+        <v>6794.971479</v>
       </c>
       <c r="H157" t="n">
-        <v>8431.283912999999</v>
+        <v>8479.639745</v>
       </c>
       <c r="I157" t="n">
-        <v>9640.455395999999</v>
+        <v>9771.047563</v>
       </c>
       <c r="J157" t="n">
         <v>26979.349244</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>206993.828918</v>
+        <v>207001.074471</v>
       </c>
       <c r="F158" t="n">
-        <v>174480.297163</v>
+        <v>174501.55505</v>
       </c>
       <c r="G158" t="n">
-        <v>168173.797021</v>
+        <v>168231.676925</v>
       </c>
       <c r="H158" t="n">
-        <v>168950.262844</v>
+        <v>169098.414173</v>
       </c>
       <c r="I158" t="n">
-        <v>170764.399803</v>
+        <v>171190.580657</v>
       </c>
       <c r="J158" t="n">
         <v>236251.757276</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1788.428626</v>
+        <v>1789.412989</v>
       </c>
       <c r="F159" t="n">
-        <v>1640.874534</v>
+        <v>1643.131724</v>
       </c>
       <c r="G159" t="n">
-        <v>1767.698157</v>
+        <v>1772.595994</v>
       </c>
       <c r="H159" t="n">
-        <v>1931.3337</v>
+        <v>1942.046688</v>
       </c>
       <c r="I159" t="n">
-        <v>2096.230688</v>
+        <v>2124.033952</v>
       </c>
       <c r="J159" t="n">
         <v>5745.849388</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>435072.483973</v>
+        <v>434936.450015</v>
       </c>
       <c r="F160" t="n">
-        <v>429796.298924</v>
+        <v>429474.52435</v>
       </c>
       <c r="G160" t="n">
-        <v>508791.467313</v>
+        <v>508068.859332</v>
       </c>
       <c r="H160" t="n">
-        <v>614316.1498369999</v>
+        <v>612684.001516</v>
       </c>
       <c r="I160" t="n">
-        <v>712018.2022610001</v>
+        <v>707687.557816</v>
       </c>
       <c r="J160" t="n">
         <v>290163.394034</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>12.626589</v>
+        <v>12.770363</v>
       </c>
       <c r="F162" t="n">
-        <v>15.216332</v>
+        <v>15.467729</v>
       </c>
       <c r="G162" t="n">
-        <v>21.638375</v>
+        <v>22.060607</v>
       </c>
       <c r="H162" t="n">
-        <v>36.060441</v>
+        <v>36.836498</v>
       </c>
       <c r="I162" t="n">
-        <v>86.455566</v>
+        <v>88.43747</v>
       </c>
       <c r="J162" t="n">
         <v>16404.918874</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4137.192109</v>
+        <v>4137.201063</v>
       </c>
       <c r="F163" t="n">
-        <v>4857.982426</v>
+        <v>4858.011586</v>
       </c>
       <c r="G163" t="n">
-        <v>6743.790029</v>
+        <v>6743.878822</v>
       </c>
       <c r="H163" t="n">
-        <v>8586.51</v>
+        <v>8586.750051999999</v>
       </c>
       <c r="I163" t="n">
-        <v>10435.999146</v>
+        <v>10436.752097</v>
       </c>
       <c r="J163" t="n">
         <v>19038.133676</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>129337.744723</v>
+        <v>129337.268363</v>
       </c>
       <c r="F164" t="n">
-        <v>165879.24959</v>
+        <v>165877.764622</v>
       </c>
       <c r="G164" t="n">
-        <v>244674.099728</v>
+        <v>244669.826522</v>
       </c>
       <c r="H164" t="n">
-        <v>333353.860343</v>
+        <v>333342.466149</v>
       </c>
       <c r="I164" t="n">
-        <v>433937.374913</v>
+        <v>433901.060304</v>
       </c>
       <c r="J164" t="n">
         <v>217390.135096</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>109773.336334</v>
+        <v>109772.887809</v>
       </c>
       <c r="F165" t="n">
-        <v>125317.062675</v>
+        <v>125315.802648</v>
       </c>
       <c r="G165" t="n">
-        <v>148852.217681</v>
+        <v>148849.247836</v>
       </c>
       <c r="H165" t="n">
-        <v>172008.880411</v>
+        <v>172002.066735</v>
       </c>
       <c r="I165" t="n">
-        <v>201944.789652</v>
+        <v>201924.985292</v>
       </c>
       <c r="J165" t="n">
         <v>69478.634993</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>468759.403605</v>
+        <v>468757.272701</v>
       </c>
       <c r="F166" t="n">
-        <v>498789.948899</v>
+        <v>498784.349161</v>
       </c>
       <c r="G166" t="n">
-        <v>607923.003556</v>
+        <v>607909.476236</v>
       </c>
       <c r="H166" t="n">
-        <v>713896.638068</v>
+        <v>713865.137983</v>
       </c>
       <c r="I166" t="n">
-        <v>828829.485356</v>
+        <v>828738.975496</v>
       </c>
       <c r="J166" t="n">
         <v>198531.996194</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>75571.476389</v>
+        <v>75574.01072000001</v>
       </c>
       <c r="F167" t="n">
-        <v>77238.52561300001</v>
+        <v>77245.034251</v>
       </c>
       <c r="G167" t="n">
-        <v>92732.34308799999</v>
+        <v>92748.011792</v>
       </c>
       <c r="H167" t="n">
-        <v>111693.002237</v>
+        <v>111730.697805</v>
       </c>
       <c r="I167" t="n">
-        <v>139066.86412</v>
+        <v>139181.976821</v>
       </c>
       <c r="J167" t="n">
         <v>1222436.268802</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1262.307334</v>
+        <v>1262.313111</v>
       </c>
       <c r="F168" t="n">
-        <v>1410.398885</v>
+        <v>1410.415693</v>
       </c>
       <c r="G168" t="n">
-        <v>1806.90932</v>
+        <v>1806.953726</v>
       </c>
       <c r="H168" t="n">
-        <v>2231.276431</v>
+        <v>2231.388464</v>
       </c>
       <c r="I168" t="n">
-        <v>2744.766028</v>
+        <v>2745.113728</v>
       </c>
       <c r="J168" t="n">
         <v>6575.490022</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>791842.133345</v>
+        <v>791839.96586</v>
       </c>
       <c r="F169" t="n">
-        <v>866240.9695229999</v>
+        <v>866235.187999</v>
       </c>
       <c r="G169" t="n">
-        <v>1089786.520059</v>
+        <v>1089772.229409</v>
       </c>
       <c r="H169" t="n">
-        <v>1372705.29915</v>
+        <v>1372669.971191</v>
       </c>
       <c r="I169" t="n">
-        <v>1770292.240431</v>
+        <v>1770180.94055</v>
       </c>
       <c r="J169" t="n">
         <v>1278717.96393</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>35520.462381</v>
+        <v>35520.461928</v>
       </c>
       <c r="F170" t="n">
-        <v>48835.957219</v>
+        <v>48835.983329</v>
       </c>
       <c r="G170" t="n">
-        <v>73202.147293</v>
+        <v>73202.287621</v>
       </c>
       <c r="H170" t="n">
-        <v>99558.941683</v>
+        <v>99559.434395</v>
       </c>
       <c r="I170" t="n">
-        <v>129416.865976</v>
+        <v>129418.698485</v>
       </c>
       <c r="J170" t="n">
         <v>183834.553821</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>76114.221796</v>
+        <v>76114.976899</v>
       </c>
       <c r="F171" t="n">
-        <v>80862.28185699999</v>
+        <v>80864.340786</v>
       </c>
       <c r="G171" t="n">
-        <v>98769.444118</v>
+        <v>98774.57412600001</v>
       </c>
       <c r="H171" t="n">
-        <v>116364.58764</v>
+        <v>116376.824812</v>
       </c>
       <c r="I171" t="n">
-        <v>136699.735434</v>
+        <v>136735.661258</v>
       </c>
       <c r="J171" t="n">
         <v>471994.184534</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>14747.463836</v>
+        <v>14750.065727</v>
       </c>
       <c r="F172" t="n">
-        <v>15213.927166</v>
+        <v>15220.623896</v>
       </c>
       <c r="G172" t="n">
-        <v>17692.697248</v>
+        <v>17708.034628</v>
       </c>
       <c r="H172" t="n">
-        <v>20463.186509</v>
+        <v>20497.415072</v>
       </c>
       <c r="I172" t="n">
-        <v>25828.655584</v>
+        <v>25926.081737</v>
       </c>
       <c r="J172" t="n">
         <v>867938.342514</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2839.571526</v>
+        <v>2839.566217</v>
       </c>
       <c r="F173" t="n">
-        <v>3710.837282</v>
+        <v>3710.821227</v>
       </c>
       <c r="G173" t="n">
-        <v>5376.69474</v>
+        <v>5376.651013</v>
       </c>
       <c r="H173" t="n">
-        <v>7177.267922</v>
+        <v>7177.156437</v>
       </c>
       <c r="I173" t="n">
-        <v>9340.035162</v>
+        <v>9339.686760000001</v>
       </c>
       <c r="J173" t="n">
         <v>8869.302046999999</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1004229.652251</v>
+        <v>1004228.884498</v>
       </c>
       <c r="F174" t="n">
-        <v>1017787.09993</v>
+        <v>1017785.372097</v>
       </c>
       <c r="G174" t="n">
-        <v>1194264.161823</v>
+        <v>1194260.489333</v>
       </c>
       <c r="H174" t="n">
-        <v>1386751.696541</v>
+        <v>1386744.006001</v>
       </c>
       <c r="I174" t="n">
-        <v>1635769.201449</v>
+        <v>1635749.000062</v>
       </c>
       <c r="J174" t="n">
         <v>1832199.58519</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5890.969656</v>
+        <v>5890.950027</v>
       </c>
       <c r="F175" t="n">
-        <v>9067.23544</v>
+        <v>9067.163049000001</v>
       </c>
       <c r="G175" t="n">
-        <v>15443.247745</v>
+        <v>15443.009845</v>
       </c>
       <c r="H175" t="n">
-        <v>23763.994846</v>
+        <v>23763.28419</v>
       </c>
       <c r="I175" t="n">
-        <v>34949.538169</v>
+        <v>34946.998975</v>
       </c>
       <c r="J175" t="n">
         <v>23923.154543</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>499.939885</v>
+        <v>499.943948</v>
       </c>
       <c r="F176" t="n">
-        <v>478.872788</v>
+        <v>478.882596</v>
       </c>
       <c r="G176" t="n">
-        <v>556.965044</v>
+        <v>556.9880889999999</v>
       </c>
       <c r="H176" t="n">
-        <v>658.5420329999999</v>
+        <v>658.597091</v>
       </c>
       <c r="I176" t="n">
-        <v>804.879012</v>
+        <v>805.047964</v>
       </c>
       <c r="J176" t="n">
         <v>2540.937627</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>518231.112443</v>
+        <v>518231.061026</v>
       </c>
       <c r="F177" t="n">
-        <v>721416.653382</v>
+        <v>721416.957419</v>
       </c>
       <c r="G177" t="n">
-        <v>1081191.343412</v>
+        <v>1081193.393891</v>
       </c>
       <c r="H177" t="n">
-        <v>1430087.488414</v>
+        <v>1430094.917137</v>
       </c>
       <c r="I177" t="n">
-        <v>1764777.839325</v>
+        <v>1764804.409217</v>
       </c>
       <c r="J177" t="n">
         <v>2363478.318214</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1257.387899</v>
+        <v>1257.396287</v>
       </c>
       <c r="F178" t="n">
-        <v>1499.820417</v>
+        <v>1499.846344</v>
       </c>
       <c r="G178" t="n">
-        <v>2012.79937</v>
+        <v>2012.87063</v>
       </c>
       <c r="H178" t="n">
-        <v>2599.855384</v>
+        <v>2600.042239</v>
       </c>
       <c r="I178" t="n">
-        <v>3340.380929</v>
+        <v>3340.983057</v>
       </c>
       <c r="J178" t="n">
         <v>10021.835238</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>868.812901</v>
+        <v>868.818452</v>
       </c>
       <c r="F179" t="n">
-        <v>911.656701</v>
+        <v>911.671692</v>
       </c>
       <c r="G179" t="n">
-        <v>1139.559982</v>
+        <v>1139.598483</v>
       </c>
       <c r="H179" t="n">
-        <v>1389.982214</v>
+        <v>1390.078018</v>
       </c>
       <c r="I179" t="n">
-        <v>1706.620506</v>
+        <v>1706.917483</v>
       </c>
       <c r="J179" t="n">
         <v>4853.778724</v>
@@ -14130,28 +14130,28 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="G181" t="n">
         <v>-1e-06</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>-5e-06</v>
       </c>
       <c r="H181" t="n">
         <v>-5e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>-2e-06</v>
+        <v>-0</v>
       </c>
       <c r="K181" t="n">
-        <v>2e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="M181" t="n">
         <v>7e-06</v>
@@ -14160,28 +14160,28 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>-0</v>
+        <v>2e-06</v>
       </c>
       <c r="P181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="S181" t="n">
         <v>-3e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="R181" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="S181" t="n">
-        <v>-2e-06</v>
       </c>
       <c r="T181" t="n">
         <v>6e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>2e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-4e-06</v>
+        <v>-2e-06</v>
       </c>
     </row>
   </sheetData>
